--- a/emargement APM4.xlsx
+++ b/emargement APM4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhoar\IdeaProjects\OasisTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05448A-D36D-4C32-A25E-4652391E9AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB455764-A0A2-4BC8-BB5D-96E65F2A8C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7245" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OASIS" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="513">
   <si>
     <t>Séance</t>
   </si>
@@ -1571,17 +1571,27 @@
   </si>
   <si>
     <t>00283</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1661,22 +1671,23 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Neutre" xfId="1" builtinId="28"/>
@@ -2020,6 +2031,9 @@
         <f>'00283'!H2</f>
         <v>aalhanbali</v>
       </c>
+      <c r="C2" s="9" t="s">
+        <v>512</v>
+      </c>
       <c r="D2" s="7" t="str">
         <f>IF('00283'!K2="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2033,6 +2047,10 @@
         <f>'00283'!H3</f>
         <v>aalloncle</v>
       </c>
+      <c r="C3" s="9" t="str">
+        <f>C2</f>
+        <v>B</v>
+      </c>
       <c r="D3" s="7" t="str">
         <f>IF('00283'!K3="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2046,6 +2064,10 @@
         <f>'00283'!H4</f>
         <v>abrucker</v>
       </c>
+      <c r="C4" s="9" t="str">
+        <f t="shared" ref="C4:C67" si="0">C3</f>
+        <v>B</v>
+      </c>
       <c r="D4" s="7" t="str">
         <f>IF('00283'!K4="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2059,6 +2081,10 @@
         <f>'00283'!H5</f>
         <v>adaussy</v>
       </c>
+      <c r="C5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D5" s="7" t="str">
         <f>IF('00283'!K5="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2072,6 +2098,10 @@
         <f>'00283'!H6</f>
         <v>adeguerines</v>
       </c>
+      <c r="C6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D6" s="7" t="str">
         <f>IF('00283'!K6="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2085,6 +2115,10 @@
         <f>'00283'!H7</f>
         <v>adimitriadis</v>
       </c>
+      <c r="C7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D7" s="7" t="str">
         <f>IF('00283'!K7="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2098,6 +2132,10 @@
         <f>'00283'!H8</f>
         <v>adivaret</v>
       </c>
+      <c r="C8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D8" s="7" t="str">
         <f>IF('00283'!K8="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2111,6 +2149,10 @@
         <f>'00283'!H9</f>
         <v>aespinoza</v>
       </c>
+      <c r="C9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D9" s="7" t="str">
         <f>IF('00283'!K9="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2124,6 +2166,10 @@
         <f>'00283'!H10</f>
         <v>agleize</v>
       </c>
+      <c r="C10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D10" s="7" t="str">
         <f>IF('00283'!K10="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2137,6 +2183,10 @@
         <f>'00283'!H11</f>
         <v>agraniromero</v>
       </c>
+      <c r="C11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D11" s="7" t="str">
         <f>IF('00283'!K11="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2150,6 +2200,10 @@
         <f>'00283'!H12</f>
         <v>ainial</v>
       </c>
+      <c r="C12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D12" s="7" t="str">
         <f>IF('00283'!K12="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2163,6 +2217,10 @@
         <f>'00283'!H13</f>
         <v>ajeong</v>
       </c>
+      <c r="C13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D13" s="7" t="str">
         <f>IF('00283'!K13="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2176,6 +2234,10 @@
         <f>'00283'!H14</f>
         <v>akuchinski</v>
       </c>
+      <c r="C14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D14" s="7" t="str">
         <f>IF('00283'!K14="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2189,6 +2251,10 @@
         <f>'00283'!H15</f>
         <v>amackay</v>
       </c>
+      <c r="C15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D15" s="7" t="str">
         <f>IF('00283'!K15="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2202,6 +2268,10 @@
         <f>'00283'!H16</f>
         <v>amarillier</v>
       </c>
+      <c r="C16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D16" s="7" t="str">
         <f>IF('00283'!K16="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2215,6 +2285,10 @@
         <f>'00283'!H17</f>
         <v>amoreira</v>
       </c>
+      <c r="C17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D17" s="7" t="str">
         <f>IF('00283'!K17="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2228,6 +2302,10 @@
         <f>'00283'!H18</f>
         <v>anakaya</v>
       </c>
+      <c r="C18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D18" s="7" t="str">
         <f>IF('00283'!K18="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2241,6 +2319,10 @@
         <f>'00283'!H19</f>
         <v>aolech</v>
       </c>
+      <c r="C19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D19" s="7" t="str">
         <f>IF('00283'!K19="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2254,6 +2336,10 @@
         <f>'00283'!H20</f>
         <v>aouary</v>
       </c>
+      <c r="C20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D20" s="7" t="str">
         <f>IF('00283'!K20="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2267,6 +2353,10 @@
         <f>'00283'!H21</f>
         <v>arinaudo</v>
       </c>
+      <c r="C21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D21" s="7" t="str">
         <f>IF('00283'!K21="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2280,6 +2370,10 @@
         <f>'00283'!H22</f>
         <v>ateyssonnieredegramont</v>
       </c>
+      <c r="C22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D22" s="7" t="str">
         <f>IF('00283'!K22="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2293,6 +2387,10 @@
         <f>'00283'!H23</f>
         <v>aueki</v>
       </c>
+      <c r="C23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D23" s="7" t="str">
         <f>IF('00283'!K23="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2306,6 +2404,10 @@
         <f>'00283'!H24</f>
         <v>avu</v>
       </c>
+      <c r="C24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D24" s="7" t="str">
         <f>IF('00283'!K24="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2319,6 +2421,10 @@
         <f>'00283'!H25</f>
         <v>bdegrande</v>
       </c>
+      <c r="C25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D25" s="7" t="str">
         <f>IF('00283'!K25="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2332,6 +2438,10 @@
         <f>'00283'!H26</f>
         <v>bdonadio</v>
       </c>
+      <c r="C26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D26" s="7" t="str">
         <f>IF('00283'!K26="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2345,6 +2455,10 @@
         <f>'00283'!H27</f>
         <v>bnaji</v>
       </c>
+      <c r="C27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D27" s="7" t="str">
         <f>IF('00283'!K27="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2358,6 +2472,10 @@
         <f>'00283'!H28</f>
         <v>calbardier</v>
       </c>
+      <c r="C28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D28" s="7" t="str">
         <f>IF('00283'!K28="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2371,6 +2489,10 @@
         <f>'00283'!H29</f>
         <v>cbrevot</v>
       </c>
+      <c r="C29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D29" s="7" t="str">
         <f>IF('00283'!K29="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2384,6 +2506,10 @@
         <f>'00283'!H30</f>
         <v>cdebellefroid</v>
       </c>
+      <c r="C30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D30" s="7" t="str">
         <f>IF('00283'!K30="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2397,6 +2523,10 @@
         <f>'00283'!H31</f>
         <v>cdespres</v>
       </c>
+      <c r="C31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D31" s="7" t="str">
         <f>IF('00283'!K31="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2410,6 +2540,10 @@
         <f>'00283'!H32</f>
         <v>cfohr</v>
       </c>
+      <c r="C32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D32" s="7" t="str">
         <f>IF('00283'!K32="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2423,6 +2557,10 @@
         <f>'00283'!H33</f>
         <v>cgrimaud</v>
       </c>
+      <c r="C33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D33" s="7" t="str">
         <f>IF('00283'!K33="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2436,6 +2574,10 @@
         <f>'00283'!H34</f>
         <v>cmons</v>
       </c>
+      <c r="C34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D34" s="7" t="str">
         <f>IF('00283'!K34="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2449,6 +2591,10 @@
         <f>'00283'!H35</f>
         <v>cmoreau1</v>
       </c>
+      <c r="C35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D35" s="7" t="str">
         <f>IF('00283'!K35="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2462,6 +2608,10 @@
         <f>'00283'!H36</f>
         <v>conaran</v>
       </c>
+      <c r="C36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D36" s="7" t="str">
         <f>IF('00283'!K36="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2475,6 +2625,10 @@
         <f>'00283'!H37</f>
         <v>cperrot</v>
       </c>
+      <c r="C37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D37" s="7" t="str">
         <f>IF('00283'!K37="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2488,6 +2642,10 @@
         <f>'00283'!H38</f>
         <v>croudier</v>
       </c>
+      <c r="C38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D38" s="7" t="str">
         <f>IF('00283'!K38="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2501,6 +2659,10 @@
         <f>'00283'!H39</f>
         <v>csaunierbouyssier</v>
       </c>
+      <c r="C39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D39" s="7" t="str">
         <f>IF('00283'!K39="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2514,6 +2676,10 @@
         <f>'00283'!H40</f>
         <v>cteissedre</v>
       </c>
+      <c r="C40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D40" s="7" t="str">
         <f>IF('00283'!K40="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2527,6 +2693,10 @@
         <f>'00283'!H41</f>
         <v>cturcant</v>
       </c>
+      <c r="C41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D41" s="7" t="str">
         <f>IF('00283'!K41="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2540,6 +2710,10 @@
         <f>'00283'!H42</f>
         <v>cvandier</v>
       </c>
+      <c r="C42" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D42" s="7" t="str">
         <f>IF('00283'!K42="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2553,6 +2727,10 @@
         <f>'00283'!H43</f>
         <v>ddilay</v>
       </c>
+      <c r="C43" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D43" s="7" t="str">
         <f>IF('00283'!K43="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2566,6 +2744,10 @@
         <f>'00283'!H44</f>
         <v>dkim1</v>
       </c>
+      <c r="C44" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D44" s="7" t="str">
         <f>IF('00283'!K44="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2579,6 +2761,10 @@
         <f>'00283'!H45</f>
         <v>dneuburger</v>
       </c>
+      <c r="C45" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D45" s="7" t="str">
         <f>IF('00283'!K45="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2592,6 +2778,10 @@
         <f>'00283'!H46</f>
         <v>dsheng</v>
       </c>
+      <c r="C46" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D46" s="7" t="str">
         <f>IF('00283'!K46="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2605,6 +2795,10 @@
         <f>'00283'!H47</f>
         <v>dstreicher1</v>
       </c>
+      <c r="C47" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D47" s="7" t="str">
         <f>IF('00283'!K47="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2618,6 +2812,10 @@
         <f>'00283'!H48</f>
         <v>dwang1</v>
       </c>
+      <c r="C48" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D48" s="7" t="str">
         <f>IF('00283'!K48="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2631,6 +2829,10 @@
         <f>'00283'!H49</f>
         <v>eassuied</v>
       </c>
+      <c r="C49" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D49" s="7" t="str">
         <f>IF('00283'!K49="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2644,6 +2846,10 @@
         <f>'00283'!H50</f>
         <v>ebai</v>
       </c>
+      <c r="C50" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D50" s="7" t="str">
         <f>IF('00283'!K50="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2657,6 +2863,10 @@
         <f>'00283'!H51</f>
         <v>ebontoux</v>
       </c>
+      <c r="C51" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D51" s="7" t="str">
         <f>IF('00283'!K51="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2670,6 +2880,10 @@
         <f>'00283'!H52</f>
         <v>ecarreno</v>
       </c>
+      <c r="C52" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D52" s="7" t="str">
         <f>IF('00283'!K52="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2683,6 +2897,10 @@
         <f>'00283'!H53</f>
         <v>eclem</v>
       </c>
+      <c r="C53" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D53" s="7" t="str">
         <f>IF('00283'!K53="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2696,6 +2914,10 @@
         <f>'00283'!H54</f>
         <v>eforster1</v>
       </c>
+      <c r="C54" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D54" s="7" t="str">
         <f>IF('00283'!K54="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2709,6 +2931,10 @@
         <f>'00283'!H55</f>
         <v>egrandcolas</v>
       </c>
+      <c r="C55" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D55" s="7" t="str">
         <f>IF('00283'!K55="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2722,6 +2948,10 @@
         <f>'00283'!H56</f>
         <v>elefaure</v>
       </c>
+      <c r="C56" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D56" s="7" t="str">
         <f>IF('00283'!K56="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2735,6 +2965,10 @@
         <f>'00283'!H57</f>
         <v>epamelard</v>
       </c>
+      <c r="C57" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D57" s="7" t="str">
         <f>IF('00283'!K57="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2748,6 +2982,10 @@
         <f>'00283'!H58</f>
         <v>ereuze</v>
       </c>
+      <c r="C58" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D58" s="7" t="str">
         <f>IF('00283'!K58="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2761,6 +2999,10 @@
         <f>'00283'!H59</f>
         <v>esigrist</v>
       </c>
+      <c r="C59" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D59" s="7" t="str">
         <f>IF('00283'!K59="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2774,6 +3016,10 @@
         <f>'00283'!H60</f>
         <v>fklingelschmitt</v>
       </c>
+      <c r="C60" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D60" s="7" t="str">
         <f>IF('00283'!K60="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2787,6 +3033,10 @@
         <f>'00283'!H61</f>
         <v>flebleis</v>
       </c>
+      <c r="C61" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D61" s="7" t="str">
         <f>IF('00283'!K61="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2800,6 +3050,10 @@
         <f>'00283'!H62</f>
         <v>fmarconnet</v>
       </c>
+      <c r="C62" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D62" s="7" t="str">
         <f>IF('00283'!K62="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2813,6 +3067,10 @@
         <f>'00283'!H63</f>
         <v>fmikkola</v>
       </c>
+      <c r="C63" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D63" s="7" t="str">
         <f>IF('00283'!K63="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2826,6 +3084,10 @@
         <f>'00283'!H64</f>
         <v>gaggeler</v>
       </c>
+      <c r="C64" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D64" s="7" t="str">
         <f>IF('00283'!K64="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2839,6 +3101,10 @@
         <f>'00283'!H65</f>
         <v>ggarciasanchez</v>
       </c>
+      <c r="C65" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D65" s="7" t="str">
         <f>IF('00283'!K65="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2852,6 +3118,10 @@
         <f>'00283'!H66</f>
         <v>gjazeron</v>
       </c>
+      <c r="C66" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D66" s="7" t="str">
         <f>IF('00283'!K66="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2865,6 +3135,10 @@
         <f>'00283'!H67</f>
         <v>gkeller</v>
       </c>
+      <c r="C67" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
       <c r="D67" s="7" t="str">
         <f>IF('00283'!K67="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2878,6 +3152,10 @@
         <f>'00283'!H68</f>
         <v>gpstepowski</v>
       </c>
+      <c r="C68" s="9" t="str">
+        <f t="shared" ref="C68:C131" si="1">C67</f>
+        <v>B</v>
+      </c>
       <c r="D68" s="7" t="str">
         <f>IF('00283'!K68="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2891,6 +3169,10 @@
         <f>'00283'!H69</f>
         <v>gwei</v>
       </c>
+      <c r="C69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D69" s="7" t="str">
         <f>IF('00283'!K69="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2904,6 +3186,10 @@
         <f>'00283'!H70</f>
         <v>hgambard</v>
       </c>
+      <c r="C70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D70" s="7" t="str">
         <f>IF('00283'!K70="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2917,6 +3203,10 @@
         <f>'00283'!H71</f>
         <v>hlassalle</v>
       </c>
+      <c r="C71" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D71" s="7" t="str">
         <f>IF('00283'!K71="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2930,6 +3220,10 @@
         <f>'00283'!H72</f>
         <v>hsatotellier</v>
       </c>
+      <c r="C72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D72" s="7" t="str">
         <f>IF('00283'!K72="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2943,6 +3237,10 @@
         <f>'00283'!H73</f>
         <v>ieljamri</v>
       </c>
+      <c r="C73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D73" s="7" t="str">
         <f>IF('00283'!K73="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2956,6 +3254,10 @@
         <f>'00283'!H74</f>
         <v>imaciuca</v>
       </c>
+      <c r="C74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D74" s="7" t="str">
         <f>IF('00283'!K74="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -2969,6 +3271,10 @@
         <f>'00283'!H75</f>
         <v>jbdemaria</v>
       </c>
+      <c r="C75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D75" s="7" t="str">
         <f>IF('00283'!K75="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2982,6 +3288,10 @@
         <f>'00283'!H76</f>
         <v>jbrau</v>
       </c>
+      <c r="C76" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D76" s="7" t="str">
         <f>IF('00283'!K76="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -2995,6 +3305,10 @@
         <f>'00283'!H77</f>
         <v>jhe</v>
       </c>
+      <c r="C77" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D77" s="7" t="str">
         <f>IF('00283'!K77="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3008,6 +3322,10 @@
         <f>'00283'!H78</f>
         <v>jlee1</v>
       </c>
+      <c r="C78" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D78" s="7" t="str">
         <f>IF('00283'!K78="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3021,6 +3339,10 @@
         <f>'00283'!H79</f>
         <v>jmialon</v>
       </c>
+      <c r="C79" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D79" s="7" t="str">
         <f>IF('00283'!K79="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3034,6 +3356,10 @@
         <f>'00283'!H80</f>
         <v>jpminassian</v>
       </c>
+      <c r="C80" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D80" s="7" t="str">
         <f>IF('00283'!K80="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3047,6 +3373,10 @@
         <f>'00283'!H81</f>
         <v>jqi</v>
       </c>
+      <c r="C81" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D81" s="7" t="str">
         <f>IF('00283'!K81="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3060,6 +3390,10 @@
         <f>'00283'!H82</f>
         <v>jsohn</v>
       </c>
+      <c r="C82" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D82" s="7" t="str">
         <f>IF('00283'!K82="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3073,6 +3407,10 @@
         <f>'00283'!H83</f>
         <v>karboleda</v>
       </c>
+      <c r="C83" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D83" s="7" t="str">
         <f>IF('00283'!K83="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3086,6 +3424,10 @@
         <f>'00283'!H84</f>
         <v>kcamus</v>
       </c>
+      <c r="C84" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D84" s="7" t="str">
         <f>IF('00283'!K84="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3099,6 +3441,10 @@
         <f>'00283'!H85</f>
         <v>khko</v>
       </c>
+      <c r="C85" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D85" s="7" t="str">
         <f>IF('00283'!K85="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3112,6 +3458,10 @@
         <f>'00283'!H86</f>
         <v>ksun1</v>
       </c>
+      <c r="C86" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D86" s="7" t="str">
         <f>IF('00283'!K86="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3125,6 +3475,10 @@
         <f>'00283'!H87</f>
         <v>lchifman</v>
       </c>
+      <c r="C87" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D87" s="7" t="str">
         <f>IF('00283'!K87="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3138,6 +3492,10 @@
         <f>'00283'!H88</f>
         <v>lcouralet</v>
       </c>
+      <c r="C88" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D88" s="7" t="str">
         <f>IF('00283'!K88="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3151,6 +3509,10 @@
         <f>'00283'!H89</f>
         <v>ldegallerydelaserviere</v>
       </c>
+      <c r="C89" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D89" s="7" t="str">
         <f>IF('00283'!K89="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3164,6 +3526,10 @@
         <f>'00283'!H90</f>
         <v>lfittipaldi</v>
       </c>
+      <c r="C90" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D90" s="7" t="str">
         <f>IF('00283'!K90="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3177,6 +3543,10 @@
         <f>'00283'!H91</f>
         <v>llesecq</v>
       </c>
+      <c r="C91" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D91" s="7" t="str">
         <f>IF('00283'!K91="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3190,6 +3560,10 @@
         <f>'00283'!H92</f>
         <v>lmanquillet</v>
       </c>
+      <c r="C92" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D92" s="7" t="str">
         <f>IF('00283'!K92="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3203,6 +3577,10 @@
         <f>'00283'!H93</f>
         <v>lmonteils</v>
       </c>
+      <c r="C93" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D93" s="7" t="str">
         <f>IF('00283'!K93="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3216,6 +3594,10 @@
         <f>'00283'!H94</f>
         <v>lmstoger</v>
       </c>
+      <c r="C94" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D94" s="7" t="str">
         <f>IF('00283'!K94="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3229,6 +3611,10 @@
         <f>'00283'!H95</f>
         <v>lpaques</v>
       </c>
+      <c r="C95" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D95" s="7" t="str">
         <f>IF('00283'!K95="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3242,6 +3628,10 @@
         <f>'00283'!H96</f>
         <v>lromandevesa</v>
       </c>
+      <c r="C96" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D96" s="7" t="str">
         <f>IF('00283'!K96="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3255,6 +3645,10 @@
         <f>'00283'!H97</f>
         <v>lszymonik</v>
       </c>
+      <c r="C97" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D97" s="7" t="str">
         <f>IF('00283'!K97="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3268,6 +3662,10 @@
         <f>'00283'!H98</f>
         <v>mbrunet1</v>
       </c>
+      <c r="C98" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D98" s="7" t="str">
         <f>IF('00283'!K98="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3281,6 +3679,10 @@
         <f>'00283'!H99</f>
         <v>mcambon</v>
       </c>
+      <c r="C99" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D99" s="7" t="str">
         <f>IF('00283'!K99="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3294,6 +3696,10 @@
         <f>'00283'!H100</f>
         <v>mchamblas</v>
       </c>
+      <c r="C100" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D100" s="7" t="str">
         <f>IF('00283'!K100="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3307,6 +3713,10 @@
         <f>'00283'!H101</f>
         <v>mchampion</v>
       </c>
+      <c r="C101" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D101" s="7" t="str">
         <f>IF('00283'!K101="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3320,6 +3730,10 @@
         <f>'00283'!H102</f>
         <v>mcol</v>
       </c>
+      <c r="C102" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D102" s="7" t="str">
         <f>IF('00283'!K102="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3333,6 +3747,10 @@
         <f>'00283'!H103</f>
         <v>mdevane</v>
       </c>
+      <c r="C103" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D103" s="7" t="str">
         <f>IF('00283'!K103="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3346,6 +3764,10 @@
         <f>'00283'!H104</f>
         <v>mfiorina</v>
       </c>
+      <c r="C104" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D104" s="7" t="str">
         <f>IF('00283'!K104="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3359,6 +3781,10 @@
         <f>'00283'!H105</f>
         <v>mgheribi</v>
       </c>
+      <c r="C105" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D105" s="7" t="str">
         <f>IF('00283'!K105="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3372,6 +3798,10 @@
         <f>'00283'!H106</f>
         <v>mgostijanovic</v>
       </c>
+      <c r="C106" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D106" s="7" t="str">
         <f>IF('00283'!K106="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3385,6 +3815,10 @@
         <f>'00283'!H107</f>
         <v>mlatarjet</v>
       </c>
+      <c r="C107" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D107" s="7" t="str">
         <f>IF('00283'!K107="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3398,6 +3832,10 @@
         <f>'00283'!H108</f>
         <v>mlintanf</v>
       </c>
+      <c r="C108" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D108" s="7" t="str">
         <f>IF('00283'!K108="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3411,6 +3849,10 @@
         <f>'00283'!H109</f>
         <v>mmichel1</v>
       </c>
+      <c r="C109" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D109" s="7" t="str">
         <f>IF('00283'!K109="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3424,6 +3866,10 @@
         <f>'00283'!H110</f>
         <v>moga</v>
       </c>
+      <c r="C110" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D110" s="7" t="str">
         <f>IF('00283'!K110="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3437,6 +3883,10 @@
         <f>'00283'!H111</f>
         <v>mraineteau</v>
       </c>
+      <c r="C111" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D111" s="7" t="str">
         <f>IF('00283'!K111="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3450,6 +3900,10 @@
         <f>'00283'!H112</f>
         <v>mxifaras</v>
       </c>
+      <c r="C112" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D112" s="7" t="str">
         <f>IF('00283'!K112="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3463,6 +3917,10 @@
         <f>'00283'!H113</f>
         <v>myeo</v>
       </c>
+      <c r="C113" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D113" s="7" t="str">
         <f>IF('00283'!K113="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3476,6 +3934,10 @@
         <f>'00283'!H114</f>
         <v>mzaichikova</v>
       </c>
+      <c r="C114" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D114" s="7" t="str">
         <f>IF('00283'!K114="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3489,6 +3951,10 @@
         <f>'00283'!H115</f>
         <v>mzinchenko</v>
       </c>
+      <c r="C115" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D115" s="7" t="str">
         <f>IF('00283'!K115="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3502,6 +3968,10 @@
         <f>'00283'!H116</f>
         <v>nasama</v>
       </c>
+      <c r="C116" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D116" s="7" t="str">
         <f>IF('00283'!K116="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3515,6 +3985,10 @@
         <f>'00283'!H117</f>
         <v>nbernel</v>
       </c>
+      <c r="C117" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D117" s="7" t="str">
         <f>IF('00283'!K117="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3528,6 +4002,10 @@
         <f>'00283'!H118</f>
         <v>ndebart</v>
       </c>
+      <c r="C118" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D118" s="7" t="str">
         <f>IF('00283'!K118="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3541,6 +4019,10 @@
         <f>'00283'!H119</f>
         <v>nnoufel</v>
       </c>
+      <c r="C119" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D119" s="7" t="str">
         <f>IF('00283'!K119="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3554,6 +4036,10 @@
         <f>'00283'!H120</f>
         <v>norbach</v>
       </c>
+      <c r="C120" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D120" s="7" t="str">
         <f>IF('00283'!K120="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3567,6 +4053,10 @@
         <f>'00283'!H121</f>
         <v>nqueyrouxdagostino</v>
       </c>
+      <c r="C121" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D121" s="7" t="str">
         <f>IF('00283'!K121="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3580,6 +4070,10 @@
         <f>'00283'!H122</f>
         <v>nreynaud</v>
       </c>
+      <c r="C122" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D122" s="7" t="str">
         <f>IF('00283'!K122="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3593,6 +4087,10 @@
         <f>'00283'!H123</f>
         <v>ohatzfeld</v>
       </c>
+      <c r="C123" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D123" s="7" t="str">
         <f>IF('00283'!K123="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3606,6 +4104,10 @@
         <f>'00283'!H124</f>
         <v>olavignolle</v>
       </c>
+      <c r="C124" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D124" s="7" t="str">
         <f>IF('00283'!K124="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3619,6 +4121,10 @@
         <f>'00283'!H125</f>
         <v>parenioult</v>
       </c>
+      <c r="C125" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D125" s="7" t="str">
         <f>IF('00283'!K125="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3632,6 +4138,10 @@
         <f>'00283'!H126</f>
         <v>pberny</v>
       </c>
+      <c r="C126" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D126" s="7" t="str">
         <f>IF('00283'!K126="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3645,6 +4155,10 @@
         <f>'00283'!H127</f>
         <v>plecocq</v>
       </c>
+      <c r="C127" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D127" s="7" t="str">
         <f>IF('00283'!K127="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3658,6 +4172,10 @@
         <f>'00283'!H128</f>
         <v>prenaudinvary</v>
       </c>
+      <c r="C128" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D128" s="7" t="str">
         <f>IF('00283'!K128="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3671,6 +4189,10 @@
         <f>'00283'!H129</f>
         <v>pterreaux</v>
       </c>
+      <c r="C129" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D129" s="7" t="str">
         <f>IF('00283'!K129="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3684,6 +4206,10 @@
         <f>'00283'!H130</f>
         <v>pzadlo</v>
       </c>
+      <c r="C130" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D130" s="7" t="str">
         <f>IF('00283'!K130="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3697,6 +4223,10 @@
         <f>'00283'!H131</f>
         <v>rcornus</v>
       </c>
+      <c r="C131" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
       <c r="D131" s="7" t="str">
         <f>IF('00283'!K131="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3710,6 +4240,10 @@
         <f>'00283'!H132</f>
         <v>rfilipe</v>
       </c>
+      <c r="C132" s="9" t="str">
+        <f t="shared" ref="C132:C169" si="2">C131</f>
+        <v>B</v>
+      </c>
       <c r="D132" s="7" t="str">
         <f>IF('00283'!K132="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3723,6 +4257,10 @@
         <f>'00283'!H133</f>
         <v>rlebre</v>
       </c>
+      <c r="C133" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D133" s="7" t="str">
         <f>IF('00283'!K133="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3736,6 +4274,10 @@
         <f>'00283'!H134</f>
         <v>rpogam</v>
       </c>
+      <c r="C134" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D134" s="7" t="str">
         <f>IF('00283'!K134="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3749,6 +4291,10 @@
         <f>'00283'!H135</f>
         <v>rwinckels</v>
       </c>
+      <c r="C135" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D135" s="7" t="str">
         <f>IF('00283'!K135="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3762,6 +4308,10 @@
         <f>'00283'!H136</f>
         <v>sbounechada</v>
       </c>
+      <c r="C136" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D136" s="7" t="str">
         <f>IF('00283'!K136="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3775,6 +4325,10 @@
         <f>'00283'!H137</f>
         <v>sclausse</v>
       </c>
+      <c r="C137" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D137" s="7" t="str">
         <f>IF('00283'!K137="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3788,6 +4342,10 @@
         <f>'00283'!H138</f>
         <v>sfrancoiselie</v>
       </c>
+      <c r="C138" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D138" s="7" t="str">
         <f>IF('00283'!K138="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3801,6 +4359,10 @@
         <f>'00283'!H139</f>
         <v>sgalzin</v>
       </c>
+      <c r="C139" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D139" s="7" t="str">
         <f>IF('00283'!K139="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3814,6 +4376,10 @@
         <f>'00283'!H140</f>
         <v>smorin</v>
       </c>
+      <c r="C140" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D140" s="7" t="str">
         <f>IF('00283'!K140="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3827,6 +4393,10 @@
         <f>'00283'!H141</f>
         <v>sprieurblanc</v>
       </c>
+      <c r="C141" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D141" s="7" t="str">
         <f>IF('00283'!K141="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3840,6 +4410,10 @@
         <f>'00283'!H142</f>
         <v>sthan</v>
       </c>
+      <c r="C142" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D142" s="7" t="str">
         <f>IF('00283'!K142="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3853,6 +4427,10 @@
         <f>'00283'!H143</f>
         <v>takuo</v>
       </c>
+      <c r="C143" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D143" s="7" t="str">
         <f>IF('00283'!K143="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3866,6 +4444,10 @@
         <f>'00283'!H144</f>
         <v>tclu</v>
       </c>
+      <c r="C144" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D144" s="7" t="str">
         <f>IF('00283'!K144="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3879,6 +4461,10 @@
         <f>'00283'!H145</f>
         <v>tcupolillo</v>
       </c>
+      <c r="C145" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D145" s="7" t="str">
         <f>IF('00283'!K145="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3892,6 +4478,10 @@
         <f>'00283'!H146</f>
         <v>tfajoles</v>
       </c>
+      <c r="C146" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D146" s="7" t="str">
         <f>IF('00283'!K146="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3905,6 +4495,10 @@
         <f>'00283'!H147</f>
         <v>tgaillard</v>
       </c>
+      <c r="C147" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D147" s="7" t="str">
         <f>IF('00283'!K147="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3918,6 +4512,10 @@
         <f>'00283'!H148</f>
         <v>tjen</v>
       </c>
+      <c r="C148" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D148" s="7" t="str">
         <f>IF('00283'!K148="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3931,6 +4529,10 @@
         <f>'00283'!H149</f>
         <v>tkamogawa</v>
       </c>
+      <c r="C149" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D149" s="7" t="str">
         <f>IF('00283'!K149="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3944,6 +4546,10 @@
         <f>'00283'!H150</f>
         <v>tmazaud</v>
       </c>
+      <c r="C150" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D150" s="7" t="str">
         <f>IF('00283'!K150="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3957,6 +4563,10 @@
         <f>'00283'!H151</f>
         <v>tmazoyer</v>
       </c>
+      <c r="C151" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D151" s="7" t="str">
         <f>IF('00283'!K151="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3970,6 +4580,10 @@
         <f>'00283'!H152</f>
         <v>tprechal</v>
       </c>
+      <c r="C152" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D152" s="7" t="str">
         <f>IF('00283'!K152="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -3983,6 +4597,10 @@
         <f>'00283'!H153</f>
         <v>tquarre</v>
       </c>
+      <c r="C153" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D153" s="7" t="str">
         <f>IF('00283'!K153="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -3996,6 +4614,10 @@
         <f>'00283'!H154</f>
         <v>trezzouk</v>
       </c>
+      <c r="C154" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D154" s="7" t="str">
         <f>IF('00283'!K154="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -4009,6 +4631,10 @@
         <f>'00283'!H155</f>
         <v>vcampean</v>
       </c>
+      <c r="C155" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D155" s="7" t="str">
         <f>IF('00283'!K155="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4022,6 +4648,10 @@
         <f>'00283'!H156</f>
         <v>vcandalot</v>
       </c>
+      <c r="C156" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D156" s="7" t="str">
         <f>IF('00283'!K156="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4035,6 +4665,10 @@
         <f>'00283'!H157</f>
         <v>vmedojevic</v>
       </c>
+      <c r="C157" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D157" s="7" t="str">
         <f>IF('00283'!K157="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -4048,6 +4682,10 @@
         <f>'00283'!H158</f>
         <v>wjkim</v>
       </c>
+      <c r="C158" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D158" s="7" t="str">
         <f>IF('00283'!K158="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4061,6 +4699,10 @@
         <f>'00283'!H159</f>
         <v>wwinterstin</v>
       </c>
+      <c r="C159" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D159" s="7" t="str">
         <f>IF('00283'!K159="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4074,6 +4716,10 @@
         <f>'00283'!H160</f>
         <v>ybayeul</v>
       </c>
+      <c r="C160" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D160" s="7" t="str">
         <f>IF('00283'!K160="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -4087,6 +4733,10 @@
         <f>'00283'!H161</f>
         <v>ycaels</v>
       </c>
+      <c r="C161" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D161" s="7" t="str">
         <f>IF('00283'!K161="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4100,6 +4750,10 @@
         <f>'00283'!H162</f>
         <v>ychoi</v>
       </c>
+      <c r="C162" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D162" s="7" t="str">
         <f>IF('00283'!K162="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4113,6 +4767,10 @@
         <f>'00283'!H163</f>
         <v>yduchemin</v>
       </c>
+      <c r="C163" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D163" s="7" t="str">
         <f>IF('00283'!K163="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -4126,6 +4784,10 @@
         <f>'00283'!H164</f>
         <v>yhasegawa</v>
       </c>
+      <c r="C164" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D164" s="7" t="str">
         <f>IF('00283'!K164="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -4139,6 +4801,10 @@
         <f>'00283'!H165</f>
         <v>yhuot</v>
       </c>
+      <c r="C165" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D165" s="7" t="str">
         <f>IF('00283'!K165="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4152,6 +4818,10 @@
         <f>'00283'!H166</f>
         <v>ylkuo</v>
       </c>
+      <c r="C166" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D166" s="7" t="str">
         <f>IF('00283'!K166="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4165,6 +4835,10 @@
         <f>'00283'!H167</f>
         <v>ywang3</v>
       </c>
+      <c r="C167" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D167" s="7" t="str">
         <f>IF('00283'!K167="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4178,6 +4852,10 @@
         <f>'00283'!H168</f>
         <v>yychang</v>
       </c>
+      <c r="C168" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D168" s="7" t="str">
         <f>IF('00283'!K168="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
@@ -4191,6 +4869,10 @@
         <f>'00283'!H169</f>
         <v>zcatta</v>
       </c>
+      <c r="C169" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
       <c r="D169" s="7" t="str">
         <f>IF('00283'!K169="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
@@ -5049,7 +5731,7 @@
       <c r="B382" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/emargement APM4.xlsx
+++ b/emargement APM4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhoar\IdeaProjects\OasisTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB455764-A0A2-4BC8-BB5D-96E65F2A8C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81028868-F30B-4E2E-89F1-343D178AD5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="34560" windowHeight="18648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OASIS" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="512">
   <si>
     <t>Séance</t>
   </si>
@@ -1571,9 +1571,6 @@
   </si>
   <si>
     <t>00283</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
 </sst>
 </file>
@@ -1996,17 +1993,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF0EEC3-C9FE-4980-868B-CA572A553C6F}">
   <dimension ref="A1:E382"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" style="7"/>
+    <col min="2" max="2" width="12.77734375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" style="7"/>
     <col min="5" max="5" width="15" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="10.90625" style="7"/>
+    <col min="6" max="16384" width="10.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>506</v>
       </c>
@@ -2023,7 +2020,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>511</v>
       </c>
@@ -2031,15 +2028,16 @@
         <f>'00283'!H2</f>
         <v>aalhanbali</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>512</v>
+      <c r="C2" s="9" t="str">
+        <f t="shared" ref="C2:C65" si="0">IF(D2="VALIDATE","B","U")</f>
+        <v>B</v>
       </c>
       <c r="D2" s="7" t="str">
         <f>IF('00283'!K2="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>511</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>aalloncle</v>
       </c>
       <c r="C3" s="9" t="str">
-        <f>C2</f>
+        <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="D3" s="7" t="str">
@@ -2056,7 +2054,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>511</v>
       </c>
@@ -2065,7 +2063,7 @@
         <v>abrucker</v>
       </c>
       <c r="C4" s="9" t="str">
-        <f t="shared" ref="C4:C67" si="0">C3</f>
+        <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="D4" s="7" t="str">
@@ -2073,7 +2071,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>511</v>
       </c>
@@ -2082,15 +2080,15 @@
         <v>adaussy</v>
       </c>
       <c r="C5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f>IF(D5="VALIDATE","B","")</f>
+        <v/>
       </c>
       <c r="D5" s="7" t="str">
         <f>IF('00283'!K5="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>511</v>
       </c>
@@ -2099,7 +2097,7 @@
         <v>adeguerines</v>
       </c>
       <c r="C6" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C6:C69" si="1">IF(D6="VALIDATE","B","")</f>
         <v>B</v>
       </c>
       <c r="D6" s="7" t="str">
@@ -2107,7 +2105,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>511</v>
       </c>
@@ -2116,7 +2114,7 @@
         <v>adimitriadis</v>
       </c>
       <c r="C7" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D7" s="7" t="str">
@@ -2124,7 +2122,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>511</v>
       </c>
@@ -2133,15 +2131,15 @@
         <v>adivaret</v>
       </c>
       <c r="C8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D8" s="7" t="str">
         <f>IF('00283'!K8="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>511</v>
       </c>
@@ -2150,7 +2148,7 @@
         <v>aespinoza</v>
       </c>
       <c r="C9" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D9" s="7" t="str">
@@ -2158,7 +2156,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>511</v>
       </c>
@@ -2167,7 +2165,7 @@
         <v>agleize</v>
       </c>
       <c r="C10" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D10" s="7" t="str">
@@ -2175,7 +2173,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>511</v>
       </c>
@@ -2184,7 +2182,7 @@
         <v>agraniromero</v>
       </c>
       <c r="C11" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D11" s="7" t="str">
@@ -2192,7 +2190,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>511</v>
       </c>
@@ -2201,7 +2199,7 @@
         <v>ainial</v>
       </c>
       <c r="C12" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D12" s="7" t="str">
@@ -2209,7 +2207,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>511</v>
       </c>
@@ -2218,15 +2216,15 @@
         <v>ajeong</v>
       </c>
       <c r="C13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D13" s="7" t="str">
         <f>IF('00283'!K13="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>511</v>
       </c>
@@ -2235,7 +2233,7 @@
         <v>akuchinski</v>
       </c>
       <c r="C14" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D14" s="7" t="str">
@@ -2243,7 +2241,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>511</v>
       </c>
@@ -2252,15 +2250,15 @@
         <v>amackay</v>
       </c>
       <c r="C15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D15" s="7" t="str">
         <f>IF('00283'!K15="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>511</v>
       </c>
@@ -2269,15 +2267,15 @@
         <v>amarillier</v>
       </c>
       <c r="C16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D16" s="7" t="str">
         <f>IF('00283'!K16="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>511</v>
       </c>
@@ -2286,7 +2284,7 @@
         <v>amoreira</v>
       </c>
       <c r="C17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D17" s="7" t="str">
@@ -2294,7 +2292,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>511</v>
       </c>
@@ -2303,7 +2301,7 @@
         <v>anakaya</v>
       </c>
       <c r="C18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D18" s="7" t="str">
@@ -2311,7 +2309,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>511</v>
       </c>
@@ -2320,15 +2318,15 @@
         <v>aolech</v>
       </c>
       <c r="C19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D19" s="7" t="str">
         <f>IF('00283'!K19="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>511</v>
       </c>
@@ -2337,7 +2335,7 @@
         <v>aouary</v>
       </c>
       <c r="C20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D20" s="7" t="str">
@@ -2345,7 +2343,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>511</v>
       </c>
@@ -2354,7 +2352,7 @@
         <v>arinaudo</v>
       </c>
       <c r="C21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D21" s="7" t="str">
@@ -2362,7 +2360,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>511</v>
       </c>
@@ -2371,15 +2369,15 @@
         <v>ateyssonnieredegramont</v>
       </c>
       <c r="C22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D22" s="7" t="str">
         <f>IF('00283'!K22="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>511</v>
       </c>
@@ -2388,7 +2386,7 @@
         <v>aueki</v>
       </c>
       <c r="C23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D23" s="7" t="str">
@@ -2396,7 +2394,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>511</v>
       </c>
@@ -2405,15 +2403,15 @@
         <v>avu</v>
       </c>
       <c r="C24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D24" s="7" t="str">
         <f>IF('00283'!K24="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>511</v>
       </c>
@@ -2422,7 +2420,7 @@
         <v>bdegrande</v>
       </c>
       <c r="C25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D25" s="7" t="str">
@@ -2430,7 +2428,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>511</v>
       </c>
@@ -2439,7 +2437,7 @@
         <v>bdonadio</v>
       </c>
       <c r="C26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D26" s="7" t="str">
@@ -2447,7 +2445,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>511</v>
       </c>
@@ -2456,15 +2454,15 @@
         <v>bnaji</v>
       </c>
       <c r="C27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D27" s="7" t="str">
         <f>IF('00283'!K27="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>511</v>
       </c>
@@ -2473,15 +2471,15 @@
         <v>calbardier</v>
       </c>
       <c r="C28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D28" s="7" t="str">
         <f>IF('00283'!K28="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>511</v>
       </c>
@@ -2490,15 +2488,15 @@
         <v>cbrevot</v>
       </c>
       <c r="C29" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D29" s="7" t="str">
         <f>IF('00283'!K29="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>511</v>
       </c>
@@ -2507,15 +2505,15 @@
         <v>cdebellefroid</v>
       </c>
       <c r="C30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D30" s="7" t="str">
         <f>IF('00283'!K30="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>511</v>
       </c>
@@ -2524,7 +2522,7 @@
         <v>cdespres</v>
       </c>
       <c r="C31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D31" s="7" t="str">
@@ -2532,7 +2530,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>511</v>
       </c>
@@ -2541,7 +2539,7 @@
         <v>cfohr</v>
       </c>
       <c r="C32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D32" s="7" t="str">
@@ -2549,7 +2547,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>511</v>
       </c>
@@ -2558,15 +2556,15 @@
         <v>cgrimaud</v>
       </c>
       <c r="C33" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D33" s="7" t="str">
         <f>IF('00283'!K33="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>511</v>
       </c>
@@ -2575,15 +2573,15 @@
         <v>cmons</v>
       </c>
       <c r="C34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D34" s="7" t="str">
         <f>IF('00283'!K34="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>511</v>
       </c>
@@ -2592,15 +2590,15 @@
         <v>cmoreau1</v>
       </c>
       <c r="C35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D35" s="7" t="str">
         <f>IF('00283'!K35="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>511</v>
       </c>
@@ -2609,7 +2607,7 @@
         <v>conaran</v>
       </c>
       <c r="C36" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D36" s="7" t="str">
@@ -2617,7 +2615,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>511</v>
       </c>
@@ -2626,7 +2624,7 @@
         <v>cperrot</v>
       </c>
       <c r="C37" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D37" s="7" t="str">
@@ -2634,7 +2632,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>511</v>
       </c>
@@ -2643,7 +2641,7 @@
         <v>croudier</v>
       </c>
       <c r="C38" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D38" s="7" t="str">
@@ -2651,7 +2649,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>511</v>
       </c>
@@ -2660,7 +2658,7 @@
         <v>csaunierbouyssier</v>
       </c>
       <c r="C39" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D39" s="7" t="str">
@@ -2668,7 +2666,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>511</v>
       </c>
@@ -2677,7 +2675,7 @@
         <v>cteissedre</v>
       </c>
       <c r="C40" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D40" s="7" t="str">
@@ -2685,7 +2683,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>511</v>
       </c>
@@ -2694,7 +2692,7 @@
         <v>cturcant</v>
       </c>
       <c r="C41" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D41" s="7" t="str">
@@ -2702,7 +2700,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>511</v>
       </c>
@@ -2711,15 +2709,15 @@
         <v>cvandier</v>
       </c>
       <c r="C42" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D42" s="7" t="str">
         <f>IF('00283'!K42="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>511</v>
       </c>
@@ -2728,7 +2726,7 @@
         <v>ddilay</v>
       </c>
       <c r="C43" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D43" s="7" t="str">
@@ -2736,7 +2734,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>511</v>
       </c>
@@ -2745,7 +2743,7 @@
         <v>dkim1</v>
       </c>
       <c r="C44" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D44" s="7" t="str">
@@ -2753,7 +2751,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>511</v>
       </c>
@@ -2762,15 +2760,15 @@
         <v>dneuburger</v>
       </c>
       <c r="C45" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D45" s="7" t="str">
         <f>IF('00283'!K45="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>511</v>
       </c>
@@ -2779,7 +2777,7 @@
         <v>dsheng</v>
       </c>
       <c r="C46" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D46" s="7" t="str">
@@ -2787,7 +2785,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>511</v>
       </c>
@@ -2796,15 +2794,15 @@
         <v>dstreicher1</v>
       </c>
       <c r="C47" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D47" s="7" t="str">
         <f>IF('00283'!K47="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>511</v>
       </c>
@@ -2813,15 +2811,15 @@
         <v>dwang1</v>
       </c>
       <c r="C48" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D48" s="7" t="str">
         <f>IF('00283'!K48="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>511</v>
       </c>
@@ -2830,15 +2828,15 @@
         <v>eassuied</v>
       </c>
       <c r="C49" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D49" s="7" t="str">
         <f>IF('00283'!K49="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>511</v>
       </c>
@@ -2847,7 +2845,7 @@
         <v>ebai</v>
       </c>
       <c r="C50" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D50" s="7" t="str">
@@ -2855,7 +2853,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>511</v>
       </c>
@@ -2864,7 +2862,7 @@
         <v>ebontoux</v>
       </c>
       <c r="C51" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D51" s="7" t="str">
@@ -2872,7 +2870,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>511</v>
       </c>
@@ -2881,7 +2879,7 @@
         <v>ecarreno</v>
       </c>
       <c r="C52" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D52" s="7" t="str">
@@ -2889,7 +2887,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>511</v>
       </c>
@@ -2898,7 +2896,7 @@
         <v>eclem</v>
       </c>
       <c r="C53" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D53" s="7" t="str">
@@ -2906,7 +2904,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>511</v>
       </c>
@@ -2915,7 +2913,7 @@
         <v>eforster1</v>
       </c>
       <c r="C54" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D54" s="7" t="str">
@@ -2923,7 +2921,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>511</v>
       </c>
@@ -2932,15 +2930,15 @@
         <v>egrandcolas</v>
       </c>
       <c r="C55" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D55" s="7" t="str">
         <f>IF('00283'!K55="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>511</v>
       </c>
@@ -2949,15 +2947,15 @@
         <v>elefaure</v>
       </c>
       <c r="C56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D56" s="7" t="str">
         <f>IF('00283'!K56="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>511</v>
       </c>
@@ -2966,15 +2964,15 @@
         <v>epamelard</v>
       </c>
       <c r="C57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D57" s="7" t="str">
         <f>IF('00283'!K57="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>511</v>
       </c>
@@ -2983,7 +2981,7 @@
         <v>ereuze</v>
       </c>
       <c r="C58" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D58" s="7" t="str">
@@ -2991,7 +2989,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>511</v>
       </c>
@@ -3000,15 +2998,15 @@
         <v>esigrist</v>
       </c>
       <c r="C59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D59" s="7" t="str">
         <f>IF('00283'!K59="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>511</v>
       </c>
@@ -3017,7 +3015,7 @@
         <v>fklingelschmitt</v>
       </c>
       <c r="C60" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D60" s="7" t="str">
@@ -3025,7 +3023,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>511</v>
       </c>
@@ -3034,7 +3032,7 @@
         <v>flebleis</v>
       </c>
       <c r="C61" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D61" s="7" t="str">
@@ -3042,7 +3040,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>511</v>
       </c>
@@ -3051,15 +3049,15 @@
         <v>fmarconnet</v>
       </c>
       <c r="C62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D62" s="7" t="str">
         <f>IF('00283'!K62="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>511</v>
       </c>
@@ -3068,7 +3066,7 @@
         <v>fmikkola</v>
       </c>
       <c r="C63" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D63" s="7" t="str">
@@ -3076,7 +3074,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>511</v>
       </c>
@@ -3085,15 +3083,15 @@
         <v>gaggeler</v>
       </c>
       <c r="C64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D64" s="7" t="str">
         <f>IF('00283'!K64="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>511</v>
       </c>
@@ -3102,7 +3100,7 @@
         <v>ggarciasanchez</v>
       </c>
       <c r="C65" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D65" s="7" t="str">
@@ -3110,7 +3108,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>511</v>
       </c>
@@ -3119,7 +3117,7 @@
         <v>gjazeron</v>
       </c>
       <c r="C66" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="D66" s="7" t="str">
@@ -3127,7 +3125,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>511</v>
       </c>
@@ -3136,15 +3134,15 @@
         <v>gkeller</v>
       </c>
       <c r="C67" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D67" s="7" t="str">
         <f>IF('00283'!K67="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>511</v>
       </c>
@@ -3153,15 +3151,15 @@
         <v>gpstepowski</v>
       </c>
       <c r="C68" s="9" t="str">
-        <f t="shared" ref="C68:C131" si="1">C67</f>
-        <v>B</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="D68" s="7" t="str">
         <f>IF('00283'!K68="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>511</v>
       </c>
@@ -3171,14 +3169,14 @@
       </c>
       <c r="C69" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>B</v>
+        <v/>
       </c>
       <c r="D69" s="7" t="str">
         <f>IF('00283'!K69="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>511</v>
       </c>
@@ -3187,15 +3185,15 @@
         <v>hgambard</v>
       </c>
       <c r="C70" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" ref="C70:C133" si="2">IF(D70="VALIDATE","B","")</f>
+        <v/>
       </c>
       <c r="D70" s="7" t="str">
         <f>IF('00283'!K70="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>511</v>
       </c>
@@ -3204,15 +3202,15 @@
         <v>hlassalle</v>
       </c>
       <c r="C71" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D71" s="7" t="str">
         <f>IF('00283'!K71="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>511</v>
       </c>
@@ -3221,7 +3219,7 @@
         <v>hsatotellier</v>
       </c>
       <c r="C72" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D72" s="7" t="str">
@@ -3229,7 +3227,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>511</v>
       </c>
@@ -3238,7 +3236,7 @@
         <v>ieljamri</v>
       </c>
       <c r="C73" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D73" s="7" t="str">
@@ -3246,7 +3244,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>511</v>
       </c>
@@ -3255,15 +3253,15 @@
         <v>imaciuca</v>
       </c>
       <c r="C74" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D74" s="7" t="str">
         <f>IF('00283'!K74="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>511</v>
       </c>
@@ -3272,7 +3270,7 @@
         <v>jbdemaria</v>
       </c>
       <c r="C75" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D75" s="7" t="str">
@@ -3280,7 +3278,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>511</v>
       </c>
@@ -3289,7 +3287,7 @@
         <v>jbrau</v>
       </c>
       <c r="C76" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D76" s="7" t="str">
@@ -3297,7 +3295,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>511</v>
       </c>
@@ -3306,15 +3304,15 @@
         <v>jhe</v>
       </c>
       <c r="C77" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D77" s="7" t="str">
         <f>IF('00283'!K77="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>511</v>
       </c>
@@ -3323,15 +3321,15 @@
         <v>jlee1</v>
       </c>
       <c r="C78" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D78" s="7" t="str">
         <f>IF('00283'!K78="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>511</v>
       </c>
@@ -3340,15 +3338,15 @@
         <v>jmialon</v>
       </c>
       <c r="C79" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D79" s="7" t="str">
         <f>IF('00283'!K79="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>511</v>
       </c>
@@ -3357,15 +3355,15 @@
         <v>jpminassian</v>
       </c>
       <c r="C80" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D80" s="7" t="str">
         <f>IF('00283'!K80="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>511</v>
       </c>
@@ -3374,7 +3372,7 @@
         <v>jqi</v>
       </c>
       <c r="C81" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D81" s="7" t="str">
@@ -3382,7 +3380,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>511</v>
       </c>
@@ -3391,7 +3389,7 @@
         <v>jsohn</v>
       </c>
       <c r="C82" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D82" s="7" t="str">
@@ -3399,7 +3397,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>511</v>
       </c>
@@ -3408,7 +3406,7 @@
         <v>karboleda</v>
       </c>
       <c r="C83" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D83" s="7" t="str">
@@ -3416,7 +3414,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>511</v>
       </c>
@@ -3425,15 +3423,15 @@
         <v>kcamus</v>
       </c>
       <c r="C84" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D84" s="7" t="str">
         <f>IF('00283'!K84="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>511</v>
       </c>
@@ -3442,7 +3440,7 @@
         <v>khko</v>
       </c>
       <c r="C85" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D85" s="7" t="str">
@@ -3450,7 +3448,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>511</v>
       </c>
@@ -3459,15 +3457,15 @@
         <v>ksun1</v>
       </c>
       <c r="C86" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D86" s="7" t="str">
         <f>IF('00283'!K86="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>511</v>
       </c>
@@ -3476,7 +3474,7 @@
         <v>lchifman</v>
       </c>
       <c r="C87" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D87" s="7" t="str">
@@ -3484,7 +3482,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>511</v>
       </c>
@@ -3493,15 +3491,15 @@
         <v>lcouralet</v>
       </c>
       <c r="C88" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D88" s="7" t="str">
         <f>IF('00283'!K88="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>511</v>
       </c>
@@ -3510,15 +3508,15 @@
         <v>ldegallerydelaserviere</v>
       </c>
       <c r="C89" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D89" s="7" t="str">
         <f>IF('00283'!K89="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>511</v>
       </c>
@@ -3527,15 +3525,15 @@
         <v>lfittipaldi</v>
       </c>
       <c r="C90" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D90" s="7" t="str">
         <f>IF('00283'!K90="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>511</v>
       </c>
@@ -3544,15 +3542,15 @@
         <v>llesecq</v>
       </c>
       <c r="C91" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D91" s="7" t="str">
         <f>IF('00283'!K91="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>511</v>
       </c>
@@ -3561,7 +3559,7 @@
         <v>lmanquillet</v>
       </c>
       <c r="C92" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D92" s="7" t="str">
@@ -3569,7 +3567,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>511</v>
       </c>
@@ -3578,7 +3576,7 @@
         <v>lmonteils</v>
       </c>
       <c r="C93" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D93" s="7" t="str">
@@ -3586,7 +3584,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>511</v>
       </c>
@@ -3595,7 +3593,7 @@
         <v>lmstoger</v>
       </c>
       <c r="C94" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D94" s="7" t="str">
@@ -3603,7 +3601,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>511</v>
       </c>
@@ -3612,15 +3610,15 @@
         <v>lpaques</v>
       </c>
       <c r="C95" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D95" s="7" t="str">
         <f>IF('00283'!K95="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>511</v>
       </c>
@@ -3629,7 +3627,7 @@
         <v>lromandevesa</v>
       </c>
       <c r="C96" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D96" s="7" t="str">
@@ -3637,7 +3635,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>511</v>
       </c>
@@ -3646,15 +3644,15 @@
         <v>lszymonik</v>
       </c>
       <c r="C97" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D97" s="7" t="str">
         <f>IF('00283'!K97="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>511</v>
       </c>
@@ -3663,7 +3661,7 @@
         <v>mbrunet1</v>
       </c>
       <c r="C98" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D98" s="7" t="str">
@@ -3671,7 +3669,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>511</v>
       </c>
@@ -3680,7 +3678,7 @@
         <v>mcambon</v>
       </c>
       <c r="C99" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D99" s="7" t="str">
@@ -3688,7 +3686,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>511</v>
       </c>
@@ -3697,15 +3695,15 @@
         <v>mchamblas</v>
       </c>
       <c r="C100" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D100" s="7" t="str">
         <f>IF('00283'!K100="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>511</v>
       </c>
@@ -3714,15 +3712,15 @@
         <v>mchampion</v>
       </c>
       <c r="C101" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D101" s="7" t="str">
         <f>IF('00283'!K101="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>511</v>
       </c>
@@ -3731,7 +3729,7 @@
         <v>mcol</v>
       </c>
       <c r="C102" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D102" s="7" t="str">
@@ -3739,7 +3737,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>511</v>
       </c>
@@ -3748,7 +3746,7 @@
         <v>mdevane</v>
       </c>
       <c r="C103" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D103" s="7" t="str">
@@ -3756,7 +3754,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>511</v>
       </c>
@@ -3765,7 +3763,7 @@
         <v>mfiorina</v>
       </c>
       <c r="C104" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D104" s="7" t="str">
@@ -3773,7 +3771,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>511</v>
       </c>
@@ -3782,7 +3780,7 @@
         <v>mgheribi</v>
       </c>
       <c r="C105" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D105" s="7" t="str">
@@ -3790,7 +3788,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>511</v>
       </c>
@@ -3799,7 +3797,7 @@
         <v>mgostijanovic</v>
       </c>
       <c r="C106" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D106" s="7" t="str">
@@ -3807,7 +3805,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>511</v>
       </c>
@@ -3816,15 +3814,15 @@
         <v>mlatarjet</v>
       </c>
       <c r="C107" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D107" s="7" t="str">
         <f>IF('00283'!K107="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>511</v>
       </c>
@@ -3833,15 +3831,15 @@
         <v>mlintanf</v>
       </c>
       <c r="C108" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D108" s="7" t="str">
         <f>IF('00283'!K108="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>511</v>
       </c>
@@ -3850,15 +3848,15 @@
         <v>mmichel1</v>
       </c>
       <c r="C109" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D109" s="7" t="str">
         <f>IF('00283'!K109="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>511</v>
       </c>
@@ -3867,7 +3865,7 @@
         <v>moga</v>
       </c>
       <c r="C110" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D110" s="7" t="str">
@@ -3875,7 +3873,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>511</v>
       </c>
@@ -3884,7 +3882,7 @@
         <v>mraineteau</v>
       </c>
       <c r="C111" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D111" s="7" t="str">
@@ -3892,7 +3890,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>511</v>
       </c>
@@ -3901,7 +3899,7 @@
         <v>mxifaras</v>
       </c>
       <c r="C112" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D112" s="7" t="str">
@@ -3909,7 +3907,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>511</v>
       </c>
@@ -3918,15 +3916,15 @@
         <v>myeo</v>
       </c>
       <c r="C113" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D113" s="7" t="str">
         <f>IF('00283'!K113="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>511</v>
       </c>
@@ -3935,7 +3933,7 @@
         <v>mzaichikova</v>
       </c>
       <c r="C114" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D114" s="7" t="str">
@@ -3943,7 +3941,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>511</v>
       </c>
@@ -3952,7 +3950,7 @@
         <v>mzinchenko</v>
       </c>
       <c r="C115" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D115" s="7" t="str">
@@ -3960,7 +3958,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>511</v>
       </c>
@@ -3969,7 +3967,7 @@
         <v>nasama</v>
       </c>
       <c r="C116" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D116" s="7" t="str">
@@ -3977,7 +3975,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>511</v>
       </c>
@@ -3986,7 +3984,7 @@
         <v>nbernel</v>
       </c>
       <c r="C117" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D117" s="7" t="str">
@@ -3994,7 +3992,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>511</v>
       </c>
@@ -4003,7 +4001,7 @@
         <v>ndebart</v>
       </c>
       <c r="C118" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D118" s="7" t="str">
@@ -4011,7 +4009,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>511</v>
       </c>
@@ -4020,7 +4018,7 @@
         <v>nnoufel</v>
       </c>
       <c r="C119" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D119" s="7" t="str">
@@ -4028,7 +4026,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>511</v>
       </c>
@@ -4037,15 +4035,15 @@
         <v>norbach</v>
       </c>
       <c r="C120" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D120" s="7" t="str">
         <f>IF('00283'!K120="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>511</v>
       </c>
@@ -4054,15 +4052,15 @@
         <v>nqueyrouxdagostino</v>
       </c>
       <c r="C121" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D121" s="7" t="str">
         <f>IF('00283'!K121="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>511</v>
       </c>
@@ -4071,7 +4069,7 @@
         <v>nreynaud</v>
       </c>
       <c r="C122" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D122" s="7" t="str">
@@ -4079,7 +4077,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>511</v>
       </c>
@@ -4088,7 +4086,7 @@
         <v>ohatzfeld</v>
       </c>
       <c r="C123" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D123" s="7" t="str">
@@ -4096,7 +4094,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>511</v>
       </c>
@@ -4105,7 +4103,7 @@
         <v>olavignolle</v>
       </c>
       <c r="C124" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D124" s="7" t="str">
@@ -4113,7 +4111,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>511</v>
       </c>
@@ -4122,15 +4120,15 @@
         <v>parenioult</v>
       </c>
       <c r="C125" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D125" s="7" t="str">
         <f>IF('00283'!K125="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>511</v>
       </c>
@@ -4139,15 +4137,15 @@
         <v>pberny</v>
       </c>
       <c r="C126" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D126" s="7" t="str">
         <f>IF('00283'!K126="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>511</v>
       </c>
@@ -4156,15 +4154,15 @@
         <v>plecocq</v>
       </c>
       <c r="C127" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D127" s="7" t="str">
         <f>IF('00283'!K127="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>511</v>
       </c>
@@ -4173,7 +4171,7 @@
         <v>prenaudinvary</v>
       </c>
       <c r="C128" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D128" s="7" t="str">
@@ -4181,7 +4179,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>511</v>
       </c>
@@ -4190,15 +4188,15 @@
         <v>pterreaux</v>
       </c>
       <c r="C129" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D129" s="7" t="str">
         <f>IF('00283'!K129="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>511</v>
       </c>
@@ -4207,15 +4205,15 @@
         <v>pzadlo</v>
       </c>
       <c r="C130" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D130" s="7" t="str">
         <f>IF('00283'!K130="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>511</v>
       </c>
@@ -4224,15 +4222,15 @@
         <v>rcornus</v>
       </c>
       <c r="C131" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="D131" s="7" t="str">
         <f>IF('00283'!K131="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>511</v>
       </c>
@@ -4241,7 +4239,7 @@
         <v>rfilipe</v>
       </c>
       <c r="C132" s="9" t="str">
-        <f t="shared" ref="C132:C169" si="2">C131</f>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="D132" s="7" t="str">
@@ -4249,7 +4247,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>511</v>
       </c>
@@ -4266,7 +4264,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>511</v>
       </c>
@@ -4275,15 +4273,15 @@
         <v>rpogam</v>
       </c>
       <c r="C134" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" ref="C134:C169" si="3">IF(D134="VALIDATE","B","")</f>
+        <v/>
       </c>
       <c r="D134" s="7" t="str">
         <f>IF('00283'!K134="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>511</v>
       </c>
@@ -4292,15 +4290,15 @@
         <v>rwinckels</v>
       </c>
       <c r="C135" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D135" s="7" t="str">
         <f>IF('00283'!K135="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>511</v>
       </c>
@@ -4309,7 +4307,7 @@
         <v>sbounechada</v>
       </c>
       <c r="C136" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D136" s="7" t="str">
@@ -4317,7 +4315,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>511</v>
       </c>
@@ -4326,15 +4324,15 @@
         <v>sclausse</v>
       </c>
       <c r="C137" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D137" s="7" t="str">
         <f>IF('00283'!K137="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>511</v>
       </c>
@@ -4343,15 +4341,15 @@
         <v>sfrancoiselie</v>
       </c>
       <c r="C138" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D138" s="7" t="str">
         <f>IF('00283'!K138="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>511</v>
       </c>
@@ -4360,7 +4358,7 @@
         <v>sgalzin</v>
       </c>
       <c r="C139" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D139" s="7" t="str">
@@ -4368,7 +4366,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>511</v>
       </c>
@@ -4377,15 +4375,15 @@
         <v>smorin</v>
       </c>
       <c r="C140" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D140" s="7" t="str">
         <f>IF('00283'!K140="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>511</v>
       </c>
@@ -4394,7 +4392,7 @@
         <v>sprieurblanc</v>
       </c>
       <c r="C141" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D141" s="7" t="str">
@@ -4402,7 +4400,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>511</v>
       </c>
@@ -4411,15 +4409,15 @@
         <v>sthan</v>
       </c>
       <c r="C142" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D142" s="7" t="str">
         <f>IF('00283'!K142="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>511</v>
       </c>
@@ -4428,15 +4426,15 @@
         <v>takuo</v>
       </c>
       <c r="C143" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D143" s="7" t="str">
         <f>IF('00283'!K143="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>511</v>
       </c>
@@ -4445,7 +4443,7 @@
         <v>tclu</v>
       </c>
       <c r="C144" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D144" s="7" t="str">
@@ -4453,7 +4451,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>511</v>
       </c>
@@ -4462,7 +4460,7 @@
         <v>tcupolillo</v>
       </c>
       <c r="C145" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D145" s="7" t="str">
@@ -4470,7 +4468,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>511</v>
       </c>
@@ -4479,15 +4477,15 @@
         <v>tfajoles</v>
       </c>
       <c r="C146" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D146" s="7" t="str">
         <f>IF('00283'!K146="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>511</v>
       </c>
@@ -4496,15 +4494,15 @@
         <v>tgaillard</v>
       </c>
       <c r="C147" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D147" s="7" t="str">
         <f>IF('00283'!K147="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>511</v>
       </c>
@@ -4513,7 +4511,7 @@
         <v>tjen</v>
       </c>
       <c r="C148" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D148" s="7" t="str">
@@ -4521,7 +4519,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>511</v>
       </c>
@@ -4530,7 +4528,7 @@
         <v>tkamogawa</v>
       </c>
       <c r="C149" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D149" s="7" t="str">
@@ -4538,7 +4536,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>511</v>
       </c>
@@ -4547,7 +4545,7 @@
         <v>tmazaud</v>
       </c>
       <c r="C150" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D150" s="7" t="str">
@@ -4555,7 +4553,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>511</v>
       </c>
@@ -4564,15 +4562,15 @@
         <v>tmazoyer</v>
       </c>
       <c r="C151" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D151" s="7" t="str">
         <f>IF('00283'!K151="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>511</v>
       </c>
@@ -4581,15 +4579,15 @@
         <v>tprechal</v>
       </c>
       <c r="C152" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D152" s="7" t="str">
         <f>IF('00283'!K152="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>511</v>
       </c>
@@ -4598,7 +4596,7 @@
         <v>tquarre</v>
       </c>
       <c r="C153" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D153" s="7" t="str">
@@ -4606,7 +4604,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>511</v>
       </c>
@@ -4615,15 +4613,15 @@
         <v>trezzouk</v>
       </c>
       <c r="C154" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D154" s="7" t="str">
         <f>IF('00283'!K154="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>511</v>
       </c>
@@ -4632,7 +4630,7 @@
         <v>vcampean</v>
       </c>
       <c r="C155" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D155" s="7" t="str">
@@ -4640,7 +4638,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>511</v>
       </c>
@@ -4649,7 +4647,7 @@
         <v>vcandalot</v>
       </c>
       <c r="C156" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D156" s="7" t="str">
@@ -4657,7 +4655,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>511</v>
       </c>
@@ -4666,15 +4664,15 @@
         <v>vmedojevic</v>
       </c>
       <c r="C157" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D157" s="7" t="str">
         <f>IF('00283'!K157="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>511</v>
       </c>
@@ -4683,7 +4681,7 @@
         <v>wjkim</v>
       </c>
       <c r="C158" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D158" s="7" t="str">
@@ -4691,7 +4689,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>511</v>
       </c>
@@ -4700,7 +4698,7 @@
         <v>wwinterstin</v>
       </c>
       <c r="C159" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D159" s="7" t="str">
@@ -4708,7 +4706,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>511</v>
       </c>
@@ -4717,15 +4715,15 @@
         <v>ybayeul</v>
       </c>
       <c r="C160" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D160" s="7" t="str">
         <f>IF('00283'!K160="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>511</v>
       </c>
@@ -4734,7 +4732,7 @@
         <v>ycaels</v>
       </c>
       <c r="C161" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D161" s="7" t="str">
@@ -4742,7 +4740,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>511</v>
       </c>
@@ -4751,7 +4749,7 @@
         <v>ychoi</v>
       </c>
       <c r="C162" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D162" s="7" t="str">
@@ -4759,7 +4757,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>511</v>
       </c>
@@ -4768,15 +4766,15 @@
         <v>yduchemin</v>
       </c>
       <c r="C163" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D163" s="7" t="str">
         <f>IF('00283'!K163="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>511</v>
       </c>
@@ -4785,15 +4783,15 @@
         <v>yhasegawa</v>
       </c>
       <c r="C164" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D164" s="7" t="str">
         <f>IF('00283'!K164="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>511</v>
       </c>
@@ -4802,7 +4800,7 @@
         <v>yhuot</v>
       </c>
       <c r="C165" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D165" s="7" t="str">
@@ -4810,7 +4808,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>511</v>
       </c>
@@ -4819,7 +4817,7 @@
         <v>ylkuo</v>
       </c>
       <c r="C166" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D166" s="7" t="str">
@@ -4827,7 +4825,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>511</v>
       </c>
@@ -4836,7 +4834,7 @@
         <v>ywang3</v>
       </c>
       <c r="C167" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D167" s="7" t="str">
@@ -4844,7 +4842,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>511</v>
       </c>
@@ -4853,7 +4851,7 @@
         <v>yychang</v>
       </c>
       <c r="C168" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="D168" s="7" t="str">
@@ -4861,7 +4859,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>511</v>
       </c>
@@ -4870,863 +4868,863 @@
         <v>zcatta</v>
       </c>
       <c r="C169" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="D169" s="7" t="str">
         <f>IF('00283'!K169="PRESENCE","VALIDATE","INVALIDATE")</f>
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="6"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="6"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="6"/>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="6"/>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="6"/>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="6"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="6"/>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="6"/>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="6"/>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="6"/>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="6"/>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="6"/>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="6"/>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="6"/>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="6"/>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="6"/>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="6"/>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="6"/>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="6"/>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="6"/>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="6"/>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="6"/>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="6"/>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="6"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="6"/>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="6"/>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="6"/>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="6"/>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="6"/>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="6"/>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="6"/>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="6"/>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="6"/>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="6"/>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="6"/>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="6"/>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="6"/>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="6"/>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="6"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="6"/>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="6"/>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="6"/>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="6"/>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="6"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="6"/>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="6"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="6"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="6"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="6"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="6"/>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="6"/>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="6"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="6"/>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="6"/>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="6"/>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="6"/>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="6"/>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="6"/>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="6"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="6"/>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="6"/>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="6"/>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="6"/>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="6"/>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="6"/>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="6"/>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="6"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="6"/>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="6"/>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="6"/>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="6"/>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="6"/>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="6"/>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="6"/>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="6"/>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="6"/>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="6"/>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="6"/>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="6"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="6"/>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="6"/>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="6"/>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="6"/>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="6"/>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="6"/>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="6"/>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="6"/>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="6"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="6"/>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="6"/>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="6"/>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="6"/>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="6"/>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="6"/>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="6"/>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="6"/>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="6"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="6"/>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="6"/>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="6"/>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="6"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="6"/>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="6"/>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="6"/>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="6"/>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="6"/>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="6"/>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="6"/>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="6"/>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="6"/>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="6"/>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="6"/>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="6"/>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="6"/>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="6"/>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="6"/>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="6"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="6"/>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="6"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="6"/>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="6"/>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="6"/>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="6"/>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="6"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="6"/>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="6"/>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="6"/>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="6"/>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="6"/>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="6"/>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="6"/>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
       <c r="B301" s="6"/>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
       <c r="B302" s="6"/>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
       <c r="B303" s="6"/>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
       <c r="B304" s="6"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
       <c r="B305" s="6"/>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
       <c r="B306" s="6"/>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
       <c r="B307" s="6"/>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
       <c r="B308" s="6"/>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
       <c r="B309" s="6"/>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
       <c r="B310" s="6"/>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
       <c r="B311" s="6"/>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
       <c r="B312" s="6"/>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
       <c r="B313" s="6"/>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
       <c r="B314" s="6"/>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
       <c r="B315" s="6"/>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
       <c r="B316" s="6"/>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
       <c r="B317" s="6"/>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
       <c r="B318" s="6"/>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
       <c r="B319" s="6"/>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
       <c r="B320" s="6"/>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
       <c r="B321" s="6"/>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
       <c r="B322" s="6"/>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
       <c r="B323" s="6"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
       <c r="B324" s="6"/>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
       <c r="B325" s="6"/>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
       <c r="B326" s="6"/>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
       <c r="B327" s="6"/>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
       <c r="B328" s="6"/>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
       <c r="B329" s="6"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="5"/>
       <c r="B330" s="6"/>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="5"/>
       <c r="B331" s="6"/>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="5"/>
       <c r="B332" s="6"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
       <c r="B333" s="6"/>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
       <c r="B334" s="6"/>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
       <c r="B335" s="6"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="5"/>
       <c r="B336" s="6"/>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="5"/>
       <c r="B337" s="6"/>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="5"/>
       <c r="B338" s="6"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="5"/>
       <c r="B339" s="6"/>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="5"/>
       <c r="B340" s="6"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="5"/>
       <c r="B341" s="6"/>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="5"/>
       <c r="B342" s="6"/>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="5"/>
       <c r="B343" s="6"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="5"/>
       <c r="B344" s="6"/>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="5"/>
       <c r="B345" s="6"/>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="5"/>
       <c r="B346" s="6"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="5"/>
       <c r="B347" s="6"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="5"/>
       <c r="B348" s="6"/>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="5"/>
       <c r="B349" s="6"/>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="5"/>
       <c r="B350" s="6"/>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="5"/>
       <c r="B351" s="6"/>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="5"/>
       <c r="B352" s="6"/>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="5"/>
       <c r="B353" s="6"/>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="5"/>
       <c r="B354" s="6"/>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="5"/>
       <c r="B355" s="6"/>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="5"/>
       <c r="B356" s="6"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="5"/>
       <c r="B357" s="6"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="5"/>
       <c r="B358" s="6"/>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="5"/>
       <c r="B359" s="6"/>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="5"/>
       <c r="B360" s="6"/>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="5"/>
       <c r="B361" s="6"/>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="5"/>
       <c r="B362" s="6"/>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="5"/>
       <c r="B363" s="6"/>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="5"/>
       <c r="B364" s="6"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="5"/>
       <c r="B365" s="6"/>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="5"/>
       <c r="B366" s="6"/>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="5"/>
       <c r="B367" s="6"/>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="5"/>
       <c r="B368" s="6"/>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="5"/>
       <c r="B369" s="6"/>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="5"/>
       <c r="B370" s="6"/>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="5"/>
       <c r="B371" s="6"/>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="5"/>
       <c r="B372" s="6"/>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="5"/>
       <c r="B373" s="6"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="5"/>
       <c r="B374" s="6"/>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="5"/>
       <c r="B375" s="6"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="5"/>
       <c r="B376" s="6"/>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="5"/>
       <c r="B377" s="6"/>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="5"/>
       <c r="B378" s="6"/>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="5"/>
       <c r="B379" s="6"/>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="5"/>
       <c r="B380" s="6"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="5"/>
       <c r="B381" s="6"/>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="5"/>
       <c r="B382" s="6"/>
     </row>
@@ -5740,21 +5738,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5789,7 +5787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>106559</v>
       </c>
@@ -5822,7 +5820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>106559</v>
       </c>
@@ -5855,7 +5853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>106559</v>
       </c>
@@ -5888,7 +5886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>106559</v>
       </c>
@@ -5921,7 +5919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>106559</v>
       </c>
@@ -5954,7 +5952,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>106559</v>
       </c>
@@ -5987,7 +5985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>106559</v>
       </c>
@@ -6020,7 +6018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>106559</v>
       </c>
@@ -6053,7 +6051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>106559</v>
       </c>
@@ -6086,7 +6084,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>106559</v>
       </c>
@@ -6119,7 +6117,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>106559</v>
       </c>
@@ -6152,7 +6150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>106559</v>
       </c>
@@ -6185,7 +6183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>106559</v>
       </c>
@@ -6218,7 +6216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>106559</v>
       </c>
@@ -6251,7 +6249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>106559</v>
       </c>
@@ -6284,7 +6282,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>106559</v>
       </c>
@@ -6317,7 +6315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>106559</v>
       </c>
@@ -6350,7 +6348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>106559</v>
       </c>
@@ -6383,7 +6381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>106559</v>
       </c>
@@ -6416,7 +6414,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>106559</v>
       </c>
@@ -6449,7 +6447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>106559</v>
       </c>
@@ -6482,7 +6480,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>106559</v>
       </c>
@@ -6515,7 +6513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>106559</v>
       </c>
@@ -6548,7 +6546,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>106559</v>
       </c>
@@ -6581,7 +6579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>106559</v>
       </c>
@@ -6614,7 +6612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>106559</v>
       </c>
@@ -6647,7 +6645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>106559</v>
       </c>
@@ -6680,7 +6678,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>106559</v>
       </c>
@@ -6713,7 +6711,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>106559</v>
       </c>
@@ -6746,7 +6744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>106559</v>
       </c>
@@ -6779,7 +6777,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>106559</v>
       </c>
@@ -6812,7 +6810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>106559</v>
       </c>
@@ -6845,7 +6843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>106559</v>
       </c>
@@ -6878,7 +6876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>106559</v>
       </c>
@@ -6911,7 +6909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>106559</v>
       </c>
@@ -6944,7 +6942,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>106559</v>
       </c>
@@ -6977,7 +6975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>106559</v>
       </c>
@@ -7010,7 +7008,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>106559</v>
       </c>
@@ -7043,7 +7041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>106559</v>
       </c>
@@ -7076,7 +7074,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>106559</v>
       </c>
@@ -7109,7 +7107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>106559</v>
       </c>
@@ -7142,7 +7140,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>106559</v>
       </c>
@@ -7175,7 +7173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>106559</v>
       </c>
@@ -7208,7 +7206,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>106559</v>
       </c>
@@ -7241,7 +7239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>106559</v>
       </c>
@@ -7274,7 +7272,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>106559</v>
       </c>
@@ -7307,7 +7305,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>106559</v>
       </c>
@@ -7340,7 +7338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>106559</v>
       </c>
@@ -7373,7 +7371,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>106559</v>
       </c>
@@ -7406,7 +7404,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>106559</v>
       </c>
@@ -7439,7 +7437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>106559</v>
       </c>
@@ -7472,7 +7470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>106559</v>
       </c>
@@ -7505,7 +7503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>106559</v>
       </c>
@@ -7538,7 +7536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>106559</v>
       </c>
@@ -7571,7 +7569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>106559</v>
       </c>
@@ -7604,7 +7602,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>106559</v>
       </c>
@@ -7637,7 +7635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>106559</v>
       </c>
@@ -7670,7 +7668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>106559</v>
       </c>
@@ -7703,7 +7701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>106559</v>
       </c>
@@ -7736,7 +7734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>106559</v>
       </c>
@@ -7769,7 +7767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>106559</v>
       </c>
@@ -7802,7 +7800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>106559</v>
       </c>
@@ -7835,7 +7833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>106559</v>
       </c>
@@ -7868,7 +7866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>106559</v>
       </c>
@@ -7901,7 +7899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>106559</v>
       </c>
@@ -7934,7 +7932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>106559</v>
       </c>
@@ -7967,7 +7965,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>106559</v>
       </c>
@@ -8000,7 +7998,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>106559</v>
       </c>
@@ -8033,7 +8031,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>106559</v>
       </c>
@@ -8066,7 +8064,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>106559</v>
       </c>
@@ -8099,7 +8097,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>106559</v>
       </c>
@@ -8132,7 +8130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>106559</v>
       </c>
@@ -8165,7 +8163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>106559</v>
       </c>
@@ -8198,7 +8196,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>106559</v>
       </c>
@@ -8231,7 +8229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>106559</v>
       </c>
@@ -8264,7 +8262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>106559</v>
       </c>
@@ -8297,7 +8295,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>106559</v>
       </c>
@@ -8330,7 +8328,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>106559</v>
       </c>
@@ -8363,7 +8361,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>106559</v>
       </c>
@@ -8396,7 +8394,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>106559</v>
       </c>
@@ -8429,7 +8427,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>106559</v>
       </c>
@@ -8462,7 +8460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>106559</v>
       </c>
@@ -8495,7 +8493,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>106559</v>
       </c>
@@ -8528,7 +8526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>106559</v>
       </c>
@@ -8561,7 +8559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>106559</v>
       </c>
@@ -8594,7 +8592,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>106559</v>
       </c>
@@ -8627,7 +8625,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>106559</v>
       </c>
@@ -8660,7 +8658,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>106559</v>
       </c>
@@ -8693,7 +8691,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>106559</v>
       </c>
@@ -8726,7 +8724,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>106559</v>
       </c>
@@ -8759,7 +8757,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>106559</v>
       </c>
@@ -8792,7 +8790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>106559</v>
       </c>
@@ -8825,7 +8823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>106559</v>
       </c>
@@ -8858,7 +8856,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>106559</v>
       </c>
@@ -8891,7 +8889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>106559</v>
       </c>
@@ -8924,7 +8922,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>106559</v>
       </c>
@@ -8957,7 +8955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>106559</v>
       </c>
@@ -8990,7 +8988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>106559</v>
       </c>
@@ -9023,7 +9021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>106559</v>
       </c>
@@ -9056,7 +9054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>106559</v>
       </c>
@@ -9089,7 +9087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>106559</v>
       </c>
@@ -9122,7 +9120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>106559</v>
       </c>
@@ -9155,7 +9153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>106559</v>
       </c>
@@ -9188,7 +9186,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>106559</v>
       </c>
@@ -9221,7 +9219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>106559</v>
       </c>
@@ -9254,7 +9252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>106559</v>
       </c>
@@ -9287,7 +9285,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>106559</v>
       </c>
@@ -9320,7 +9318,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>106559</v>
       </c>
@@ -9353,7 +9351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>106559</v>
       </c>
@@ -9386,7 +9384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>106559</v>
       </c>
@@ -9419,7 +9417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>106559</v>
       </c>
@@ -9452,7 +9450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>106559</v>
       </c>
@@ -9485,7 +9483,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>106559</v>
       </c>
@@ -9518,7 +9516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>106559</v>
       </c>
@@ -9551,7 +9549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>106559</v>
       </c>
@@ -9584,7 +9582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>106559</v>
       </c>
@@ -9617,7 +9615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>106559</v>
       </c>
@@ -9650,7 +9648,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>106559</v>
       </c>
@@ -9683,7 +9681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>106559</v>
       </c>
@@ -9716,7 +9714,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>106559</v>
       </c>
@@ -9749,7 +9747,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>106559</v>
       </c>
@@ -9782,7 +9780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>106559</v>
       </c>
@@ -9815,7 +9813,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>106559</v>
       </c>
@@ -9848,7 +9846,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>106559</v>
       </c>
@@ -9881,7 +9879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>106559</v>
       </c>
@@ -9914,7 +9912,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>106559</v>
       </c>
@@ -9947,7 +9945,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>106559</v>
       </c>
@@ -9980,7 +9978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>106559</v>
       </c>
@@ -10013,7 +10011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>106559</v>
       </c>
@@ -10046,7 +10044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>106559</v>
       </c>
@@ -10079,7 +10077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>106559</v>
       </c>
@@ -10112,7 +10110,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>106559</v>
       </c>
@@ -10145,7 +10143,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>106559</v>
       </c>
@@ -10178,7 +10176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>106559</v>
       </c>
@@ -10211,7 +10209,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>106559</v>
       </c>
@@ -10244,7 +10242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>106559</v>
       </c>
@@ -10277,7 +10275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>106559</v>
       </c>
@@ -10310,7 +10308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>106559</v>
       </c>
@@ -10343,7 +10341,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>106559</v>
       </c>
@@ -10376,7 +10374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>106559</v>
       </c>
@@ -10409,7 +10407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>106559</v>
       </c>
@@ -10442,7 +10440,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>106559</v>
       </c>
@@ -10475,7 +10473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>106559</v>
       </c>
@@ -10508,7 +10506,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>106559</v>
       </c>
@@ -10541,7 +10539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>106559</v>
       </c>
@@ -10574,7 +10572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>106559</v>
       </c>
@@ -10607,7 +10605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>106559</v>
       </c>
@@ -10640,7 +10638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>106559</v>
       </c>
@@ -10673,7 +10671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>106559</v>
       </c>
@@ -10706,7 +10704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>106559</v>
       </c>
@@ -10739,7 +10737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>106559</v>
       </c>
@@ -10772,7 +10770,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>106559</v>
       </c>
@@ -10805,7 +10803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>106559</v>
       </c>
@@ -10838,7 +10836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>106559</v>
       </c>
@@ -10871,7 +10869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>106559</v>
       </c>
@@ -10904,7 +10902,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>106559</v>
       </c>
@@ -10937,7 +10935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>106559</v>
       </c>
@@ -10970,7 +10968,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>106559</v>
       </c>
@@ -11003,7 +11001,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>106559</v>
       </c>
@@ -11036,7 +11034,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>106559</v>
       </c>
@@ -11069,7 +11067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>106559</v>
       </c>
@@ -11102,7 +11100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>106559</v>
       </c>
@@ -11135,7 +11133,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>106559</v>
       </c>
@@ -11168,7 +11166,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>106559</v>
       </c>
@@ -11201,7 +11199,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>106559</v>
       </c>
@@ -11234,7 +11232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>106559</v>
       </c>
@@ -11267,7 +11265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>106559</v>
       </c>
@@ -11300,7 +11298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>106559</v>
       </c>

--- a/emargement APM4.xlsx
+++ b/emargement APM4.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhoar\IdeaProjects\OasisTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB455764-A0A2-4BC8-BB5D-96E65F2A8C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADC69E3-5D93-4E6C-BFF1-B834E8B6EAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OASIS" sheetId="2" r:id="rId1"/>
     <sheet name="00283" sheetId="1" r:id="rId2"/>
+    <sheet name="sabine" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00283'!$A$1:$K$169</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="513">
   <si>
     <t>Séance</t>
   </si>
@@ -1675,7 +1676,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1688,6 +1689,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Neutre" xfId="1" builtinId="28"/>
@@ -1996,17 +1998,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF0EEC3-C9FE-4980-868B-CA572A553C6F}">
   <dimension ref="A1:E382"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.9296875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" style="7"/>
+    <col min="2" max="2" width="12.796875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.46484375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="10.9296875" style="7"/>
     <col min="5" max="5" width="15" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="10.90625" style="7"/>
+    <col min="6" max="16384" width="10.9296875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>506</v>
       </c>
@@ -2023,7 +2025,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>511</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>511</v>
       </c>
@@ -2056,7 +2058,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>511</v>
       </c>
@@ -2073,7 +2075,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>511</v>
       </c>
@@ -2087,10 +2089,10 @@
       </c>
       <c r="D5" s="7" t="str">
         <f>IF('00283'!K5="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>511</v>
       </c>
@@ -2107,7 +2109,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>511</v>
       </c>
@@ -2124,7 +2126,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>511</v>
       </c>
@@ -2141,7 +2143,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>511</v>
       </c>
@@ -2158,7 +2160,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>511</v>
       </c>
@@ -2175,7 +2177,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>511</v>
       </c>
@@ -2192,7 +2194,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>511</v>
       </c>
@@ -2209,7 +2211,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>511</v>
       </c>
@@ -2226,7 +2228,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>511</v>
       </c>
@@ -2243,7 +2245,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>511</v>
       </c>
@@ -2260,7 +2262,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>511</v>
       </c>
@@ -2274,10 +2276,10 @@
       </c>
       <c r="D16" s="7" t="str">
         <f>IF('00283'!K16="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
         <v>511</v>
       </c>
@@ -2294,7 +2296,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>511</v>
       </c>
@@ -2311,7 +2313,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>511</v>
       </c>
@@ -2328,7 +2330,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>511</v>
       </c>
@@ -2345,7 +2347,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
         <v>511</v>
       </c>
@@ -2362,7 +2364,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>511</v>
       </c>
@@ -2379,7 +2381,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
         <v>511</v>
       </c>
@@ -2396,7 +2398,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
         <v>511</v>
       </c>
@@ -2410,10 +2412,10 @@
       </c>
       <c r="D24" s="7" t="str">
         <f>IF('00283'!K24="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
         <v>511</v>
       </c>
@@ -2430,7 +2432,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
         <v>511</v>
       </c>
@@ -2447,7 +2449,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
         <v>511</v>
       </c>
@@ -2464,7 +2466,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
         <v>511</v>
       </c>
@@ -2478,10 +2480,10 @@
       </c>
       <c r="D28" s="7" t="str">
         <f>IF('00283'!K28="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
         <v>511</v>
       </c>
@@ -2495,10 +2497,10 @@
       </c>
       <c r="D29" s="7" t="str">
         <f>IF('00283'!K29="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
         <v>511</v>
       </c>
@@ -2515,7 +2517,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
         <v>511</v>
       </c>
@@ -2532,7 +2534,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
         <v>511</v>
       </c>
@@ -2549,7 +2551,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
         <v>511</v>
       </c>
@@ -2566,7 +2568,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
         <v>511</v>
       </c>
@@ -2583,7 +2585,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
         <v>511</v>
       </c>
@@ -2600,7 +2602,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="5" t="s">
         <v>511</v>
       </c>
@@ -2617,7 +2619,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
         <v>511</v>
       </c>
@@ -2634,7 +2636,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="5" t="s">
         <v>511</v>
       </c>
@@ -2651,7 +2653,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
         <v>511</v>
       </c>
@@ -2668,7 +2670,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
         <v>511</v>
       </c>
@@ -2685,7 +2687,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="5" t="s">
         <v>511</v>
       </c>
@@ -2702,7 +2704,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="5" t="s">
         <v>511</v>
       </c>
@@ -2719,7 +2721,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
         <v>511</v>
       </c>
@@ -2736,7 +2738,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="5" t="s">
         <v>511</v>
       </c>
@@ -2753,7 +2755,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="5" t="s">
         <v>511</v>
       </c>
@@ -2770,7 +2772,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="5" t="s">
         <v>511</v>
       </c>
@@ -2787,7 +2789,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="5" t="s">
         <v>511</v>
       </c>
@@ -2801,10 +2803,10 @@
       </c>
       <c r="D47" s="7" t="str">
         <f>IF('00283'!K47="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="5" t="s">
         <v>511</v>
       </c>
@@ -2821,7 +2823,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="5" t="s">
         <v>511</v>
       </c>
@@ -2838,7 +2840,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="5" t="s">
         <v>511</v>
       </c>
@@ -2855,7 +2857,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="5" t="s">
         <v>511</v>
       </c>
@@ -2872,7 +2874,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="5" t="s">
         <v>511</v>
       </c>
@@ -2889,7 +2891,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="5" t="s">
         <v>511</v>
       </c>
@@ -2906,7 +2908,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="5" t="s">
         <v>511</v>
       </c>
@@ -2923,7 +2925,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="5" t="s">
         <v>511</v>
       </c>
@@ -2940,7 +2942,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="5" t="s">
         <v>511</v>
       </c>
@@ -2957,7 +2959,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="5" t="s">
         <v>511</v>
       </c>
@@ -2974,7 +2976,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="5" t="s">
         <v>511</v>
       </c>
@@ -2991,7 +2993,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="5" t="s">
         <v>511</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="5" t="s">
         <v>511</v>
       </c>
@@ -3025,7 +3027,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="5" t="s">
         <v>511</v>
       </c>
@@ -3042,7 +3044,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="5" t="s">
         <v>511</v>
       </c>
@@ -3059,7 +3061,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="5" t="s">
         <v>511</v>
       </c>
@@ -3076,7 +3078,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="5" t="s">
         <v>511</v>
       </c>
@@ -3093,7 +3095,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="5" t="s">
         <v>511</v>
       </c>
@@ -3110,7 +3112,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="5" t="s">
         <v>511</v>
       </c>
@@ -3127,7 +3129,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="5" t="s">
         <v>511</v>
       </c>
@@ -3144,7 +3146,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="5" t="s">
         <v>511</v>
       </c>
@@ -3161,7 +3163,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="5" t="s">
         <v>511</v>
       </c>
@@ -3175,10 +3177,10 @@
       </c>
       <c r="D69" s="7" t="str">
         <f>IF('00283'!K69="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="5" t="s">
         <v>511</v>
       </c>
@@ -3192,10 +3194,10 @@
       </c>
       <c r="D70" s="7" t="str">
         <f>IF('00283'!K70="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="5" t="s">
         <v>511</v>
       </c>
@@ -3209,10 +3211,10 @@
       </c>
       <c r="D71" s="7" t="str">
         <f>IF('00283'!K71="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="5" t="s">
         <v>511</v>
       </c>
@@ -3229,7 +3231,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="5" t="s">
         <v>511</v>
       </c>
@@ -3246,7 +3248,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="5" t="s">
         <v>511</v>
       </c>
@@ -3260,10 +3262,10 @@
       </c>
       <c r="D74" s="7" t="str">
         <f>IF('00283'!K74="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="5" t="s">
         <v>511</v>
       </c>
@@ -3280,7 +3282,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="5" t="s">
         <v>511</v>
       </c>
@@ -3297,7 +3299,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="5" t="s">
         <v>511</v>
       </c>
@@ -3314,7 +3316,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="5" t="s">
         <v>511</v>
       </c>
@@ -3331,7 +3333,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="5" t="s">
         <v>511</v>
       </c>
@@ -3348,7 +3350,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="5" t="s">
         <v>511</v>
       </c>
@@ -3365,7 +3367,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="5" t="s">
         <v>511</v>
       </c>
@@ -3382,7 +3384,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="5" t="s">
         <v>511</v>
       </c>
@@ -3399,7 +3401,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="5" t="s">
         <v>511</v>
       </c>
@@ -3416,7 +3418,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="5" t="s">
         <v>511</v>
       </c>
@@ -3433,7 +3435,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="5" t="s">
         <v>511</v>
       </c>
@@ -3450,7 +3452,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="5" t="s">
         <v>511</v>
       </c>
@@ -3464,10 +3466,10 @@
       </c>
       <c r="D86" s="7" t="str">
         <f>IF('00283'!K86="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="5" t="s">
         <v>511</v>
       </c>
@@ -3484,7 +3486,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="5" t="s">
         <v>511</v>
       </c>
@@ -3501,7 +3503,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="5" t="s">
         <v>511</v>
       </c>
@@ -3518,7 +3520,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="5" t="s">
         <v>511</v>
       </c>
@@ -3532,10 +3534,10 @@
       </c>
       <c r="D90" s="7" t="str">
         <f>IF('00283'!K90="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="5" t="s">
         <v>511</v>
       </c>
@@ -3552,7 +3554,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="5" t="s">
         <v>511</v>
       </c>
@@ -3569,7 +3571,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="5" t="s">
         <v>511</v>
       </c>
@@ -3586,7 +3588,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="5" t="s">
         <v>511</v>
       </c>
@@ -3603,7 +3605,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="5" t="s">
         <v>511</v>
       </c>
@@ -3620,7 +3622,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="5" t="s">
         <v>511</v>
       </c>
@@ -3637,7 +3639,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="5" t="s">
         <v>511</v>
       </c>
@@ -3651,10 +3653,10 @@
       </c>
       <c r="D97" s="7" t="str">
         <f>IF('00283'!K97="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="5" t="s">
         <v>511</v>
       </c>
@@ -3671,7 +3673,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="5" t="s">
         <v>511</v>
       </c>
@@ -3688,7 +3690,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="5" t="s">
         <v>511</v>
       </c>
@@ -3705,7 +3707,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="5" t="s">
         <v>511</v>
       </c>
@@ -3722,7 +3724,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="5" t="s">
         <v>511</v>
       </c>
@@ -3739,7 +3741,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="5" t="s">
         <v>511</v>
       </c>
@@ -3756,7 +3758,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="5" t="s">
         <v>511</v>
       </c>
@@ -3773,7 +3775,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="5" t="s">
         <v>511</v>
       </c>
@@ -3790,7 +3792,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="5" t="s">
         <v>511</v>
       </c>
@@ -3807,7 +3809,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="5" t="s">
         <v>511</v>
       </c>
@@ -3824,7 +3826,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="5" t="s">
         <v>511</v>
       </c>
@@ -3841,7 +3843,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="5" t="s">
         <v>511</v>
       </c>
@@ -3858,7 +3860,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="5" t="s">
         <v>511</v>
       </c>
@@ -3875,7 +3877,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="5" t="s">
         <v>511</v>
       </c>
@@ -3892,7 +3894,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="5" t="s">
         <v>511</v>
       </c>
@@ -3909,7 +3911,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="5" t="s">
         <v>511</v>
       </c>
@@ -3923,10 +3925,10 @@
       </c>
       <c r="D113" s="7" t="str">
         <f>IF('00283'!K113="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="5" t="s">
         <v>511</v>
       </c>
@@ -3943,7 +3945,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="5" t="s">
         <v>511</v>
       </c>
@@ -3960,7 +3962,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="5" t="s">
         <v>511</v>
       </c>
@@ -3977,7 +3979,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="5" t="s">
         <v>511</v>
       </c>
@@ -3994,7 +3996,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="5" t="s">
         <v>511</v>
       </c>
@@ -4011,7 +4013,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" s="5" t="s">
         <v>511</v>
       </c>
@@ -4028,7 +4030,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="5" t="s">
         <v>511</v>
       </c>
@@ -4045,7 +4047,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="5" t="s">
         <v>511</v>
       </c>
@@ -4062,7 +4064,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="5" t="s">
         <v>511</v>
       </c>
@@ -4079,7 +4081,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="5" t="s">
         <v>511</v>
       </c>
@@ -4096,7 +4098,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="5" t="s">
         <v>511</v>
       </c>
@@ -4113,7 +4115,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="5" t="s">
         <v>511</v>
       </c>
@@ -4130,7 +4132,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="5" t="s">
         <v>511</v>
       </c>
@@ -4147,7 +4149,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="5" t="s">
         <v>511</v>
       </c>
@@ -4164,7 +4166,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="5" t="s">
         <v>511</v>
       </c>
@@ -4181,7 +4183,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="5" t="s">
         <v>511</v>
       </c>
@@ -4195,10 +4197,10 @@
       </c>
       <c r="D129" s="7" t="str">
         <f>IF('00283'!K129="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" s="5" t="s">
         <v>511</v>
       </c>
@@ -4215,7 +4217,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="5" t="s">
         <v>511</v>
       </c>
@@ -4232,7 +4234,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="5" t="s">
         <v>511</v>
       </c>
@@ -4249,7 +4251,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="5" t="s">
         <v>511</v>
       </c>
@@ -4266,7 +4268,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="5" t="s">
         <v>511</v>
       </c>
@@ -4280,10 +4282,10 @@
       </c>
       <c r="D134" s="7" t="str">
         <f>IF('00283'!K134="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="5" t="s">
         <v>511</v>
       </c>
@@ -4300,7 +4302,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="5" t="s">
         <v>511</v>
       </c>
@@ -4317,7 +4319,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="5" t="s">
         <v>511</v>
       </c>
@@ -4334,7 +4336,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="5" t="s">
         <v>511</v>
       </c>
@@ -4351,7 +4353,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="5" t="s">
         <v>511</v>
       </c>
@@ -4368,7 +4370,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="5" t="s">
         <v>511</v>
       </c>
@@ -4385,7 +4387,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="5" t="s">
         <v>511</v>
       </c>
@@ -4402,7 +4404,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="5" t="s">
         <v>511</v>
       </c>
@@ -4419,7 +4421,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="5" t="s">
         <v>511</v>
       </c>
@@ -4436,7 +4438,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="5" t="s">
         <v>511</v>
       </c>
@@ -4453,7 +4455,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="5" t="s">
         <v>511</v>
       </c>
@@ -4470,7 +4472,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="5" t="s">
         <v>511</v>
       </c>
@@ -4484,10 +4486,10 @@
       </c>
       <c r="D146" s="7" t="str">
         <f>IF('00283'!K146="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="5" t="s">
         <v>511</v>
       </c>
@@ -4504,7 +4506,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="5" t="s">
         <v>511</v>
       </c>
@@ -4521,7 +4523,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="5" t="s">
         <v>511</v>
       </c>
@@ -4538,7 +4540,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="5" t="s">
         <v>511</v>
       </c>
@@ -4555,7 +4557,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="5" t="s">
         <v>511</v>
       </c>
@@ -4569,10 +4571,10 @@
       </c>
       <c r="D151" s="7" t="str">
         <f>IF('00283'!K151="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="5" t="s">
         <v>511</v>
       </c>
@@ -4586,10 +4588,10 @@
       </c>
       <c r="D152" s="7" t="str">
         <f>IF('00283'!K152="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" s="5" t="s">
         <v>511</v>
       </c>
@@ -4606,7 +4608,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" s="5" t="s">
         <v>511</v>
       </c>
@@ -4623,7 +4625,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" s="5" t="s">
         <v>511</v>
       </c>
@@ -4640,7 +4642,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" s="5" t="s">
         <v>511</v>
       </c>
@@ -4657,7 +4659,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" s="5" t="s">
         <v>511</v>
       </c>
@@ -4671,10 +4673,10 @@
       </c>
       <c r="D157" s="7" t="str">
         <f>IF('00283'!K157="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A158" s="5" t="s">
         <v>511</v>
       </c>
@@ -4691,7 +4693,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" s="5" t="s">
         <v>511</v>
       </c>
@@ -4708,7 +4710,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A160" s="5" t="s">
         <v>511</v>
       </c>
@@ -4725,7 +4727,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" s="5" t="s">
         <v>511</v>
       </c>
@@ -4742,7 +4744,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="5" t="s">
         <v>511</v>
       </c>
@@ -4759,7 +4761,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" s="5" t="s">
         <v>511</v>
       </c>
@@ -4776,7 +4778,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A164" s="5" t="s">
         <v>511</v>
       </c>
@@ -4793,7 +4795,7 @@
         <v>INVALIDATE</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" s="5" t="s">
         <v>511</v>
       </c>
@@ -4810,7 +4812,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A166" s="5" t="s">
         <v>511</v>
       </c>
@@ -4827,7 +4829,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" s="5" t="s">
         <v>511</v>
       </c>
@@ -4844,7 +4846,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="5" t="s">
         <v>511</v>
       </c>
@@ -4861,7 +4863,7 @@
         <v>VALIDATE</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="5" t="s">
         <v>511</v>
       </c>
@@ -4875,858 +4877,858 @@
       </c>
       <c r="D169" s="7" t="str">
         <f>IF('00283'!K169="PRESENCE","VALIDATE","INVALIDATE")</f>
-        <v>INVALIDATE</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+        <v>VALIDATE</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" s="5"/>
       <c r="B170" s="6"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" s="5"/>
       <c r="B171" s="6"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" s="5"/>
       <c r="B172" s="6"/>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" s="5"/>
       <c r="B173" s="6"/>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" s="5"/>
       <c r="B174" s="6"/>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" s="5"/>
       <c r="B175" s="6"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" s="5"/>
       <c r="B176" s="6"/>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A177" s="5"/>
       <c r="B177" s="6"/>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A178" s="5"/>
       <c r="B178" s="6"/>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A179" s="5"/>
       <c r="B179" s="6"/>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A180" s="5"/>
       <c r="B180" s="6"/>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A181" s="5"/>
       <c r="B181" s="6"/>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A182" s="5"/>
       <c r="B182" s="6"/>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A183" s="5"/>
       <c r="B183" s="6"/>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A184" s="5"/>
       <c r="B184" s="6"/>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A185" s="5"/>
       <c r="B185" s="6"/>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A186" s="5"/>
       <c r="B186" s="6"/>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A187" s="5"/>
       <c r="B187" s="6"/>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A188" s="5"/>
       <c r="B188" s="6"/>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A189" s="5"/>
       <c r="B189" s="6"/>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A190" s="5"/>
       <c r="B190" s="6"/>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A191" s="5"/>
       <c r="B191" s="6"/>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A192" s="5"/>
       <c r="B192" s="6"/>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A193" s="5"/>
       <c r="B193" s="6"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A194" s="5"/>
       <c r="B194" s="6"/>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A195" s="5"/>
       <c r="B195" s="6"/>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A196" s="5"/>
       <c r="B196" s="6"/>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A197" s="5"/>
       <c r="B197" s="6"/>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A198" s="5"/>
       <c r="B198" s="6"/>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A199" s="5"/>
       <c r="B199" s="6"/>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A200" s="5"/>
       <c r="B200" s="6"/>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A201" s="5"/>
       <c r="B201" s="6"/>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A202" s="5"/>
       <c r="B202" s="6"/>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A203" s="5"/>
       <c r="B203" s="6"/>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A204" s="5"/>
       <c r="B204" s="6"/>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A205" s="5"/>
       <c r="B205" s="6"/>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A206" s="5"/>
       <c r="B206" s="6"/>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A207" s="5"/>
       <c r="B207" s="6"/>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A208" s="5"/>
       <c r="B208" s="6"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A209" s="5"/>
       <c r="B209" s="6"/>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A210" s="5"/>
       <c r="B210" s="6"/>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A211" s="5"/>
       <c r="B211" s="6"/>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A212" s="5"/>
       <c r="B212" s="6"/>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A213" s="5"/>
       <c r="B213" s="6"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A214" s="5"/>
       <c r="B214" s="6"/>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A215" s="5"/>
       <c r="B215" s="6"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A216" s="5"/>
       <c r="B216" s="6"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A217" s="5"/>
       <c r="B217" s="6"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A218" s="5"/>
       <c r="B218" s="6"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A219" s="5"/>
       <c r="B219" s="6"/>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A220" s="5"/>
       <c r="B220" s="6"/>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A221" s="5"/>
       <c r="B221" s="6"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A222" s="5"/>
       <c r="B222" s="6"/>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A223" s="5"/>
       <c r="B223" s="6"/>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A224" s="5"/>
       <c r="B224" s="6"/>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A225" s="5"/>
       <c r="B225" s="6"/>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A226" s="5"/>
       <c r="B226" s="6"/>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A227" s="5"/>
       <c r="B227" s="6"/>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A228" s="5"/>
       <c r="B228" s="6"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A229" s="5"/>
       <c r="B229" s="6"/>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A230" s="5"/>
       <c r="B230" s="6"/>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A231" s="5"/>
       <c r="B231" s="6"/>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A232" s="5"/>
       <c r="B232" s="6"/>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A233" s="5"/>
       <c r="B233" s="6"/>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A234" s="5"/>
       <c r="B234" s="6"/>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A235" s="5"/>
       <c r="B235" s="6"/>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A236" s="5"/>
       <c r="B236" s="6"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A237" s="5"/>
       <c r="B237" s="6"/>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A238" s="5"/>
       <c r="B238" s="6"/>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A239" s="5"/>
       <c r="B239" s="6"/>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A240" s="5"/>
       <c r="B240" s="6"/>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A241" s="5"/>
       <c r="B241" s="6"/>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A242" s="5"/>
       <c r="B242" s="6"/>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A243" s="5"/>
       <c r="B243" s="6"/>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A244" s="5"/>
       <c r="B244" s="6"/>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A245" s="5"/>
       <c r="B245" s="6"/>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A246" s="5"/>
       <c r="B246" s="6"/>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A247" s="5"/>
       <c r="B247" s="6"/>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A248" s="5"/>
       <c r="B248" s="6"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A249" s="5"/>
       <c r="B249" s="6"/>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A250" s="5"/>
       <c r="B250" s="6"/>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A251" s="5"/>
       <c r="B251" s="6"/>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A252" s="5"/>
       <c r="B252" s="6"/>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A253" s="5"/>
       <c r="B253" s="6"/>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A254" s="5"/>
       <c r="B254" s="6"/>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A255" s="5"/>
       <c r="B255" s="6"/>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A256" s="5"/>
       <c r="B256" s="6"/>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A257" s="5"/>
       <c r="B257" s="6"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A258" s="5"/>
       <c r="B258" s="6"/>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A259" s="5"/>
       <c r="B259" s="6"/>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A260" s="5"/>
       <c r="B260" s="6"/>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A261" s="5"/>
       <c r="B261" s="6"/>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A262" s="5"/>
       <c r="B262" s="6"/>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A263" s="5"/>
       <c r="B263" s="6"/>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A264" s="5"/>
       <c r="B264" s="6"/>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A265" s="5"/>
       <c r="B265" s="6"/>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A266" s="5"/>
       <c r="B266" s="6"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A267" s="5"/>
       <c r="B267" s="6"/>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A268" s="5"/>
       <c r="B268" s="6"/>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A269" s="5"/>
       <c r="B269" s="6"/>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A270" s="5"/>
       <c r="B270" s="6"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A271" s="5"/>
       <c r="B271" s="6"/>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A272" s="5"/>
       <c r="B272" s="6"/>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A273" s="5"/>
       <c r="B273" s="6"/>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A274" s="5"/>
       <c r="B274" s="6"/>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A275" s="5"/>
       <c r="B275" s="6"/>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A276" s="5"/>
       <c r="B276" s="6"/>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A277" s="5"/>
       <c r="B277" s="6"/>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A278" s="5"/>
       <c r="B278" s="6"/>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A279" s="5"/>
       <c r="B279" s="6"/>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A280" s="5"/>
       <c r="B280" s="6"/>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A281" s="5"/>
       <c r="B281" s="6"/>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A282" s="5"/>
       <c r="B282" s="6"/>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A283" s="5"/>
       <c r="B283" s="6"/>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A284" s="5"/>
       <c r="B284" s="6"/>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A285" s="5"/>
       <c r="B285" s="6"/>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A286" s="5"/>
       <c r="B286" s="6"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A287" s="5"/>
       <c r="B287" s="6"/>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A288" s="5"/>
       <c r="B288" s="6"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A289" s="5"/>
       <c r="B289" s="6"/>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A290" s="5"/>
       <c r="B290" s="6"/>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A291" s="5"/>
       <c r="B291" s="6"/>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A292" s="5"/>
       <c r="B292" s="6"/>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A293" s="5"/>
       <c r="B293" s="6"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A294" s="5"/>
       <c r="B294" s="6"/>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A295" s="5"/>
       <c r="B295" s="6"/>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A296" s="5"/>
       <c r="B296" s="6"/>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A297" s="5"/>
       <c r="B297" s="6"/>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A298" s="5"/>
       <c r="B298" s="6"/>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A299" s="5"/>
       <c r="B299" s="6"/>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A300" s="5"/>
       <c r="B300" s="6"/>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A301" s="5"/>
       <c r="B301" s="6"/>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A302" s="5"/>
       <c r="B302" s="6"/>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A303" s="5"/>
       <c r="B303" s="6"/>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A304" s="5"/>
       <c r="B304" s="6"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A305" s="5"/>
       <c r="B305" s="6"/>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A306" s="5"/>
       <c r="B306" s="6"/>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A307" s="5"/>
       <c r="B307" s="6"/>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A308" s="5"/>
       <c r="B308" s="6"/>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A309" s="5"/>
       <c r="B309" s="6"/>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A310" s="5"/>
       <c r="B310" s="6"/>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A311" s="5"/>
       <c r="B311" s="6"/>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A312" s="5"/>
       <c r="B312" s="6"/>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A313" s="5"/>
       <c r="B313" s="6"/>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A314" s="5"/>
       <c r="B314" s="6"/>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A315" s="5"/>
       <c r="B315" s="6"/>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A316" s="5"/>
       <c r="B316" s="6"/>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A317" s="5"/>
       <c r="B317" s="6"/>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A318" s="5"/>
       <c r="B318" s="6"/>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A319" s="5"/>
       <c r="B319" s="6"/>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A320" s="5"/>
       <c r="B320" s="6"/>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A321" s="5"/>
       <c r="B321" s="6"/>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A322" s="5"/>
       <c r="B322" s="6"/>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A323" s="5"/>
       <c r="B323" s="6"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A324" s="5"/>
       <c r="B324" s="6"/>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A325" s="5"/>
       <c r="B325" s="6"/>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A326" s="5"/>
       <c r="B326" s="6"/>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A327" s="5"/>
       <c r="B327" s="6"/>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A328" s="5"/>
       <c r="B328" s="6"/>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A329" s="5"/>
       <c r="B329" s="6"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A330" s="5"/>
       <c r="B330" s="6"/>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A331" s="5"/>
       <c r="B331" s="6"/>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A332" s="5"/>
       <c r="B332" s="6"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A333" s="5"/>
       <c r="B333" s="6"/>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A334" s="5"/>
       <c r="B334" s="6"/>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A335" s="5"/>
       <c r="B335" s="6"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A336" s="5"/>
       <c r="B336" s="6"/>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A337" s="5"/>
       <c r="B337" s="6"/>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A338" s="5"/>
       <c r="B338" s="6"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A339" s="5"/>
       <c r="B339" s="6"/>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A340" s="5"/>
       <c r="B340" s="6"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A341" s="5"/>
       <c r="B341" s="6"/>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A342" s="5"/>
       <c r="B342" s="6"/>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A343" s="5"/>
       <c r="B343" s="6"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A344" s="5"/>
       <c r="B344" s="6"/>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A345" s="5"/>
       <c r="B345" s="6"/>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A346" s="5"/>
       <c r="B346" s="6"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A347" s="5"/>
       <c r="B347" s="6"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A348" s="5"/>
       <c r="B348" s="6"/>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A349" s="5"/>
       <c r="B349" s="6"/>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A350" s="5"/>
       <c r="B350" s="6"/>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A351" s="5"/>
       <c r="B351" s="6"/>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A352" s="5"/>
       <c r="B352" s="6"/>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A353" s="5"/>
       <c r="B353" s="6"/>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A354" s="5"/>
       <c r="B354" s="6"/>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A355" s="5"/>
       <c r="B355" s="6"/>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A356" s="5"/>
       <c r="B356" s="6"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A357" s="5"/>
       <c r="B357" s="6"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A358" s="5"/>
       <c r="B358" s="6"/>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A359" s="5"/>
       <c r="B359" s="6"/>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A360" s="5"/>
       <c r="B360" s="6"/>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A361" s="5"/>
       <c r="B361" s="6"/>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A362" s="5"/>
       <c r="B362" s="6"/>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A363" s="5"/>
       <c r="B363" s="6"/>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A364" s="5"/>
       <c r="B364" s="6"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A365" s="5"/>
       <c r="B365" s="6"/>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A366" s="5"/>
       <c r="B366" s="6"/>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A367" s="5"/>
       <c r="B367" s="6"/>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A368" s="5"/>
       <c r="B368" s="6"/>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A369" s="5"/>
       <c r="B369" s="6"/>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A370" s="5"/>
       <c r="B370" s="6"/>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A371" s="5"/>
       <c r="B371" s="6"/>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A372" s="5"/>
       <c r="B372" s="6"/>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A373" s="5"/>
       <c r="B373" s="6"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A374" s="5"/>
       <c r="B374" s="6"/>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A375" s="5"/>
       <c r="B375" s="6"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A376" s="5"/>
       <c r="B376" s="6"/>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A377" s="5"/>
       <c r="B377" s="6"/>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A378" s="5"/>
       <c r="B378" s="6"/>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A379" s="5"/>
       <c r="B379" s="6"/>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A380" s="5"/>
       <c r="B380" s="6"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A381" s="5"/>
       <c r="B381" s="6"/>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A382" s="5"/>
       <c r="B382" s="6"/>
     </row>
@@ -5739,22 +5741,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M169"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.06640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.53125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5789,7 +5791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>106559</v>
       </c>
@@ -5821,8 +5823,16 @@
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H2,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IF(L2&lt;&gt;K2,"Diff","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>106559</v>
       </c>
@@ -5854,8 +5864,16 @@
       <c r="K3" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H3,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M66" si="0">IF(L3&lt;&gt;K3,"Diff","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>106559</v>
       </c>
@@ -5887,8 +5905,16 @@
       <c r="K4" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H4,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>106559</v>
       </c>
@@ -5918,10 +5944,18 @@
         <v>28</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L5" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H5,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>106559</v>
       </c>
@@ -5953,8 +5987,16 @@
       <c r="K6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H6,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>106559</v>
       </c>
@@ -5986,8 +6028,16 @@
       <c r="K7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H7,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>106559</v>
       </c>
@@ -6019,8 +6069,16 @@
       <c r="K8" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H8,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>106559</v>
       </c>
@@ -6052,8 +6110,16 @@
       <c r="K9" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H9,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>106559</v>
       </c>
@@ -6085,8 +6151,16 @@
       <c r="K10" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H10,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>106559</v>
       </c>
@@ -6118,8 +6192,16 @@
       <c r="K11" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H11,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>106559</v>
       </c>
@@ -6151,8 +6233,16 @@
       <c r="K12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H12,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>106559</v>
       </c>
@@ -6184,8 +6274,16 @@
       <c r="K13" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H13,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>106559</v>
       </c>
@@ -6217,8 +6315,16 @@
       <c r="K14" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H14,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>106559</v>
       </c>
@@ -6250,8 +6356,16 @@
       <c r="K15" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H15,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>106559</v>
       </c>
@@ -6281,10 +6395,18 @@
         <v>62</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L16" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H16,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>106559</v>
       </c>
@@ -6316,8 +6438,16 @@
       <c r="K17" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H17,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>106559</v>
       </c>
@@ -6349,8 +6479,16 @@
       <c r="K18" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H18,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>106559</v>
       </c>
@@ -6382,8 +6520,16 @@
       <c r="K19" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H19,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>106559</v>
       </c>
@@ -6415,8 +6561,16 @@
       <c r="K20" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H20,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>106559</v>
       </c>
@@ -6448,8 +6602,16 @@
       <c r="K21" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H21,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>106559</v>
       </c>
@@ -6481,8 +6643,16 @@
       <c r="K22" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H22,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>106559</v>
       </c>
@@ -6514,8 +6684,16 @@
       <c r="K23" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H23,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>106559</v>
       </c>
@@ -6545,10 +6723,18 @@
         <v>85</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L24" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H24,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>106559</v>
       </c>
@@ -6580,8 +6766,16 @@
       <c r="K25" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H25,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>106559</v>
       </c>
@@ -6613,8 +6807,16 @@
       <c r="K26" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L26" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H26,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>106559</v>
       </c>
@@ -6646,8 +6848,16 @@
       <c r="K27" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H27,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>106559</v>
       </c>
@@ -6677,10 +6887,18 @@
         <v>97</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L28" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H28,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>106559</v>
       </c>
@@ -6710,10 +6928,18 @@
         <v>100</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L29" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H29,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>106559</v>
       </c>
@@ -6745,8 +6971,16 @@
       <c r="K30" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L30" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H30,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>106559</v>
       </c>
@@ -6778,8 +7012,16 @@
       <c r="K31" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L31" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H31,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>106559</v>
       </c>
@@ -6811,8 +7053,16 @@
       <c r="K32" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L32" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H32,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>106559</v>
       </c>
@@ -6844,8 +7094,16 @@
       <c r="K33" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L33" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H33,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>106559</v>
       </c>
@@ -6877,8 +7135,16 @@
       <c r="K34" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L34" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H34,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>106559</v>
       </c>
@@ -6910,8 +7176,16 @@
       <c r="K35" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L35" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H35,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>106559</v>
       </c>
@@ -6943,8 +7217,16 @@
       <c r="K36" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L36" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H36,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>106559</v>
       </c>
@@ -6976,8 +7258,16 @@
       <c r="K37" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L37" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H37,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>106559</v>
       </c>
@@ -7009,8 +7299,16 @@
       <c r="K38" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L38" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H38,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>106559</v>
       </c>
@@ -7042,8 +7340,16 @@
       <c r="K39" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L39" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H39,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>106559</v>
       </c>
@@ -7075,8 +7381,16 @@
       <c r="K40" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L40" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H40,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>106559</v>
       </c>
@@ -7108,8 +7422,16 @@
       <c r="K41" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L41" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H41,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>106559</v>
       </c>
@@ -7141,8 +7463,16 @@
       <c r="K42" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L42" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H42,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M42" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>106559</v>
       </c>
@@ -7174,8 +7504,16 @@
       <c r="K43" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L43" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H43,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>106559</v>
       </c>
@@ -7207,8 +7545,16 @@
       <c r="K44" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L44" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H44,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>106559</v>
       </c>
@@ -7240,8 +7586,16 @@
       <c r="K45" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L45" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H45,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>106559</v>
       </c>
@@ -7273,8 +7627,16 @@
       <c r="K46" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L46" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H46,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>106559</v>
       </c>
@@ -7304,10 +7666,18 @@
         <v>151</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L47" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H47,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>106559</v>
       </c>
@@ -7339,8 +7709,16 @@
       <c r="K48" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L48" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H48,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>106559</v>
       </c>
@@ -7372,8 +7750,16 @@
       <c r="K49" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L49" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H49,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M49" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>106559</v>
       </c>
@@ -7405,8 +7791,16 @@
       <c r="K50" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L50" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H50,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>106559</v>
       </c>
@@ -7438,8 +7832,16 @@
       <c r="K51" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L51" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H51,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>106559</v>
       </c>
@@ -7471,8 +7873,16 @@
       <c r="K52" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L52" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H52,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>106559</v>
       </c>
@@ -7504,8 +7914,16 @@
       <c r="K53" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L53" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H53,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>106559</v>
       </c>
@@ -7537,8 +7955,16 @@
       <c r="K54" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L54" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H54,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>106559</v>
       </c>
@@ -7570,8 +7996,16 @@
       <c r="K55" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L55" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H55,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>106559</v>
       </c>
@@ -7603,8 +8037,16 @@
       <c r="K56" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L56" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H56,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>106559</v>
       </c>
@@ -7636,8 +8078,16 @@
       <c r="K57" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L57" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H57,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>106559</v>
       </c>
@@ -7669,8 +8119,16 @@
       <c r="K58" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L58" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H58,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>106559</v>
       </c>
@@ -7702,8 +8160,16 @@
       <c r="K59" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L59" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H59,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>106559</v>
       </c>
@@ -7735,8 +8201,16 @@
       <c r="K60" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L60" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H60,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>106559</v>
       </c>
@@ -7768,8 +8242,16 @@
       <c r="K61" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L61" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H61,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>106559</v>
       </c>
@@ -7801,8 +8283,16 @@
       <c r="K62" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L62" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H62,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>106559</v>
       </c>
@@ -7834,8 +8324,16 @@
       <c r="K63" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L63" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H63,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>106559</v>
       </c>
@@ -7867,8 +8365,16 @@
       <c r="K64" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L64" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H64,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M64" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>106559</v>
       </c>
@@ -7900,8 +8406,16 @@
       <c r="K65" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L65" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H65,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>106559</v>
       </c>
@@ -7933,8 +8447,16 @@
       <c r="K66" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L66" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H66,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>106559</v>
       </c>
@@ -7966,8 +8488,16 @@
       <c r="K67" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L67" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H67,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M67" t="str">
+        <f t="shared" ref="M67:M130" si="1">IF(L67&lt;&gt;K67,"Diff","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>106559</v>
       </c>
@@ -7999,8 +8529,16 @@
       <c r="K68" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L68" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H68,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>106559</v>
       </c>
@@ -8030,10 +8568,18 @@
         <v>216</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L69" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H69,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>106559</v>
       </c>
@@ -8063,10 +8609,18 @@
         <v>219</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L70" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H70,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M70" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>106559</v>
       </c>
@@ -8096,10 +8650,18 @@
         <v>222</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L71" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H71,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M71" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>106559</v>
       </c>
@@ -8131,8 +8693,16 @@
       <c r="K72" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L72" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H72,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M72" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>106559</v>
       </c>
@@ -8164,8 +8734,16 @@
       <c r="K73" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L73" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H73,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>106559</v>
       </c>
@@ -8195,10 +8773,18 @@
         <v>231</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L74" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H74,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M74" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>106559</v>
       </c>
@@ -8230,8 +8816,16 @@
       <c r="K75" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L75" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H75,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>106559</v>
       </c>
@@ -8263,8 +8857,16 @@
       <c r="K76" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L76" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H76,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M76" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>106559</v>
       </c>
@@ -8296,8 +8898,16 @@
       <c r="K77" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L77" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H77,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M77" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>106559</v>
       </c>
@@ -8329,8 +8939,16 @@
       <c r="K78" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L78" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H78,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M78" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>106559</v>
       </c>
@@ -8362,8 +8980,16 @@
       <c r="K79" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L79" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H79,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M79" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>106559</v>
       </c>
@@ -8395,8 +9021,16 @@
       <c r="K80" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L80" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H80,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>106559</v>
       </c>
@@ -8428,8 +9062,16 @@
       <c r="K81" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L81" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H81,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M81" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>106559</v>
       </c>
@@ -8461,8 +9103,16 @@
       <c r="K82" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L82" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H82,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M82" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>106559</v>
       </c>
@@ -8494,8 +9144,16 @@
       <c r="K83" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L83" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H83,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>106559</v>
       </c>
@@ -8527,8 +9185,16 @@
       <c r="K84" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L84" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H84,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>106559</v>
       </c>
@@ -8560,8 +9226,16 @@
       <c r="K85" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L85" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H85,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M85" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>106559</v>
       </c>
@@ -8591,10 +9265,18 @@
         <v>267</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L86" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H86,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M86" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>106559</v>
       </c>
@@ -8626,8 +9308,16 @@
       <c r="K87" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L87" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H87,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M87" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>106559</v>
       </c>
@@ -8659,8 +9349,16 @@
       <c r="K88" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L88" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H88,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M88" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>106559</v>
       </c>
@@ -8692,8 +9390,16 @@
       <c r="K89" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L89" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H89,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M89" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>106559</v>
       </c>
@@ -8723,10 +9429,18 @@
         <v>279</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L90" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H90,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M90" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>106559</v>
       </c>
@@ -8758,8 +9472,16 @@
       <c r="K91" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L91" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H91,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>106559</v>
       </c>
@@ -8791,8 +9513,16 @@
       <c r="K92" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L92" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H92,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M92" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>106559</v>
       </c>
@@ -8824,8 +9554,16 @@
       <c r="K93" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L93" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H93,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M93" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>106559</v>
       </c>
@@ -8857,8 +9595,16 @@
       <c r="K94" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L94" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H94,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M94" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>106559</v>
       </c>
@@ -8890,8 +9636,16 @@
       <c r="K95" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L95" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H95,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M95" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>106559</v>
       </c>
@@ -8923,8 +9677,16 @@
       <c r="K96" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L96" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H96,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M96" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>106559</v>
       </c>
@@ -8954,10 +9716,18 @@
         <v>300</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L97" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H97,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M97" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>106559</v>
       </c>
@@ -8989,8 +9759,16 @@
       <c r="K98" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L98" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H98,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>106559</v>
       </c>
@@ -9022,8 +9800,16 @@
       <c r="K99" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L99" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H99,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>106559</v>
       </c>
@@ -9055,8 +9841,16 @@
       <c r="K100" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L100" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H100,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>106559</v>
       </c>
@@ -9088,8 +9882,16 @@
       <c r="K101" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L101" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H101,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>106559</v>
       </c>
@@ -9121,8 +9923,16 @@
       <c r="K102" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L102" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H102,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>106559</v>
       </c>
@@ -9154,8 +9964,16 @@
       <c r="K103" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L103" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H103,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M103" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>106559</v>
       </c>
@@ -9187,8 +10005,16 @@
       <c r="K104" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L104" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H104,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M104" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>106559</v>
       </c>
@@ -9220,8 +10046,16 @@
       <c r="K105" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L105" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H105,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>106559</v>
       </c>
@@ -9253,8 +10087,16 @@
       <c r="K106" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L106" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H106,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>106559</v>
       </c>
@@ -9286,8 +10128,16 @@
       <c r="K107" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L107" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H107,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>106559</v>
       </c>
@@ -9319,8 +10169,16 @@
       <c r="K108" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L108" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H108,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>106559</v>
       </c>
@@ -9352,8 +10210,16 @@
       <c r="K109" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L109" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H109,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M109" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>106559</v>
       </c>
@@ -9385,8 +10251,16 @@
       <c r="K110" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L110" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H110,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M110" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>106559</v>
       </c>
@@ -9418,8 +10292,16 @@
       <c r="K111" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L111" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H111,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>106559</v>
       </c>
@@ -9451,8 +10333,16 @@
       <c r="K112" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L112" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H112,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M112" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>106559</v>
       </c>
@@ -9482,10 +10372,18 @@
         <v>347</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L113" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H113,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>106559</v>
       </c>
@@ -9517,8 +10415,16 @@
       <c r="K114" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L114" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H114,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M114" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>106559</v>
       </c>
@@ -9550,8 +10456,16 @@
       <c r="K115" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L115" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H115,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M115" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>106559</v>
       </c>
@@ -9583,8 +10497,16 @@
       <c r="K116" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L116" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H116,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>106559</v>
       </c>
@@ -9616,8 +10538,16 @@
       <c r="K117" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L117" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H117,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>106559</v>
       </c>
@@ -9649,8 +10579,16 @@
       <c r="K118" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L118" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H118,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>106559</v>
       </c>
@@ -9682,8 +10620,16 @@
       <c r="K119" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L119" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H119,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>106559</v>
       </c>
@@ -9715,8 +10661,16 @@
       <c r="K120" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L120" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H120,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>106559</v>
       </c>
@@ -9748,8 +10702,16 @@
       <c r="K121" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L121" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H121,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M121" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>106559</v>
       </c>
@@ -9781,8 +10743,16 @@
       <c r="K122" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L122" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H122,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M122" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>106559</v>
       </c>
@@ -9814,8 +10784,16 @@
       <c r="K123" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L123" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H123,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M123" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>106559</v>
       </c>
@@ -9847,8 +10825,16 @@
       <c r="K124" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L124" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H124,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M124" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>106559</v>
       </c>
@@ -9880,8 +10866,16 @@
       <c r="K125" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L125" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H125,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M125" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>106559</v>
       </c>
@@ -9913,8 +10907,16 @@
       <c r="K126" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L126" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H126,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M126" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>106559</v>
       </c>
@@ -9946,8 +10948,16 @@
       <c r="K127" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L127" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H127,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M127" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>106559</v>
       </c>
@@ -9979,8 +10989,16 @@
       <c r="K128" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L128" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H128,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M128" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>106559</v>
       </c>
@@ -10010,10 +11028,18 @@
         <v>393</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L129" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H129,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M129" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>106559</v>
       </c>
@@ -10045,8 +11071,16 @@
       <c r="K130" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L130" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H130,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M130" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>106559</v>
       </c>
@@ -10078,8 +11112,16 @@
       <c r="K131" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L131" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H131,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M131" t="str">
+        <f t="shared" ref="M131:M169" si="2">IF(L131&lt;&gt;K131,"Diff","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>106559</v>
       </c>
@@ -10111,8 +11153,16 @@
       <c r="K132" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L132" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H132,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M132" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>106559</v>
       </c>
@@ -10144,8 +11194,16 @@
       <c r="K133" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L133" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H133,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M133" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>106559</v>
       </c>
@@ -10175,10 +11233,18 @@
         <v>407</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L134" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H134,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M134" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>106559</v>
       </c>
@@ -10210,8 +11276,16 @@
       <c r="K135" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L135" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H135,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M135" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>106559</v>
       </c>
@@ -10243,8 +11317,16 @@
       <c r="K136" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L136" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H136,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M136" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
         <v>106559</v>
       </c>
@@ -10276,8 +11358,16 @@
       <c r="K137" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L137" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H137,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M137" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>106559</v>
       </c>
@@ -10309,8 +11399,16 @@
       <c r="K138" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L138" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H138,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
         <v>106559</v>
       </c>
@@ -10342,8 +11440,16 @@
       <c r="K139" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L139" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H139,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M139" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>106559</v>
       </c>
@@ -10375,8 +11481,16 @@
       <c r="K140" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L140" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H140,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M140" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>106559</v>
       </c>
@@ -10408,8 +11522,16 @@
       <c r="K141" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L141" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H141,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M141" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>106559</v>
       </c>
@@ -10441,8 +11563,16 @@
       <c r="K142" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L142" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H142,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M142" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>106559</v>
       </c>
@@ -10474,8 +11604,16 @@
       <c r="K143" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L143" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H143,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M143" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>106559</v>
       </c>
@@ -10507,8 +11645,16 @@
       <c r="K144" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L144" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H144,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M144" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>106559</v>
       </c>
@@ -10540,8 +11686,16 @@
       <c r="K145" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L145" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H145,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M145" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>106559</v>
       </c>
@@ -10571,10 +11725,18 @@
         <v>441</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L146" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H146,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M146" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>106559</v>
       </c>
@@ -10606,8 +11768,16 @@
       <c r="K147" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L147" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H147,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M147" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>106559</v>
       </c>
@@ -10639,8 +11809,16 @@
       <c r="K148" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L148" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H148,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>106559</v>
       </c>
@@ -10672,8 +11850,16 @@
       <c r="K149" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L149" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H149,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M149" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>106559</v>
       </c>
@@ -10705,8 +11891,16 @@
       <c r="K150" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L150" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H150,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M150" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>106559</v>
       </c>
@@ -10736,10 +11930,18 @@
         <v>456</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L151" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H151,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M151" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>106559</v>
       </c>
@@ -10769,10 +11971,18 @@
         <v>458</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L152" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H152,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M152" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
         <v>106559</v>
       </c>
@@ -10804,8 +12014,16 @@
       <c r="K153" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L153" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H153,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M153" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>106559</v>
       </c>
@@ -10837,8 +12055,16 @@
       <c r="K154" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L154" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H154,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M154" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>106559</v>
       </c>
@@ -10870,8 +12096,16 @@
       <c r="K155" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L155" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H155,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M155" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>106559</v>
       </c>
@@ -10903,8 +12137,16 @@
       <c r="K156" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L156" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H156,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M156" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>106559</v>
       </c>
@@ -10934,10 +12176,18 @@
         <v>472</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="L157" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H157,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M157" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>106559</v>
       </c>
@@ -10969,8 +12219,16 @@
       <c r="K158" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L158" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H158,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M158" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>106559</v>
       </c>
@@ -11002,8 +12260,16 @@
       <c r="K159" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L159" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H159,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M159" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>106559</v>
       </c>
@@ -11035,8 +12301,16 @@
       <c r="K160" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L160" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H160,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M160" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>106559</v>
       </c>
@@ -11068,8 +12342,16 @@
       <c r="K161" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L161" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H161,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M161" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>106559</v>
       </c>
@@ -11101,8 +12383,16 @@
       <c r="K162" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L162" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H162,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M162" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>106559</v>
       </c>
@@ -11134,8 +12424,16 @@
       <c r="K163" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L163" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H163,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M163" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>106559</v>
       </c>
@@ -11167,8 +12465,16 @@
       <c r="K164" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L164" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H164,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>ABSENCE</v>
+      </c>
+      <c r="M164" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>106559</v>
       </c>
@@ -11200,8 +12506,16 @@
       <c r="K165" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L165" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H165,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M165" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>106559</v>
       </c>
@@ -11233,8 +12547,16 @@
       <c r="K166" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L166" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H166,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M166" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>106559</v>
       </c>
@@ -11266,8 +12588,16 @@
       <c r="K167" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L167" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H167,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M167" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>106559</v>
       </c>
@@ -11299,8 +12629,16 @@
       <c r="K168" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L168" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H168,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M168" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>106559</v>
       </c>
@@ -11330,7 +12668,15 @@
         <v>505</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="L169" t="str">
+        <f>_xlfn.XLOOKUP('00283'!H169,sabine!D:D,sabine!G:G,"",0,1)</f>
+        <v>PRESENCE</v>
+      </c>
+      <c r="M169" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -11338,4 +12684,3374 @@
   <autoFilter ref="A1:K169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC753CD2-981A-4EB8-AC82-1CD7DA8F6EB6}">
+  <dimension ref="A1:G168"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1">
+        <v>106559</v>
+      </c>
+      <c r="C1" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>106559</v>
+      </c>
+      <c r="C2" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>106559</v>
+      </c>
+      <c r="C3" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>106559</v>
+      </c>
+      <c r="C4" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>106559</v>
+      </c>
+      <c r="C5" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>106559</v>
+      </c>
+      <c r="C6" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>106559</v>
+      </c>
+      <c r="C7" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>106559</v>
+      </c>
+      <c r="C8" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D8" t="s">
+        <v>478</v>
+      </c>
+      <c r="E8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F8" t="s">
+        <v>480</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>106559</v>
+      </c>
+      <c r="C9" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E9" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>106559</v>
+      </c>
+      <c r="C10" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D10" t="s">
+        <v>382</v>
+      </c>
+      <c r="E10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F10" t="s">
+        <v>384</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>106559</v>
+      </c>
+      <c r="C11" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>106559</v>
+      </c>
+      <c r="C12" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F12" t="s">
+        <v>413</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>106559</v>
+      </c>
+      <c r="C13" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>106559</v>
+      </c>
+      <c r="C14" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>106559</v>
+      </c>
+      <c r="C15" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>106559</v>
+      </c>
+      <c r="C16" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>106559</v>
+      </c>
+      <c r="C17" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D17" t="s">
+        <v>481</v>
+      </c>
+      <c r="E17" t="s">
+        <v>482</v>
+      </c>
+      <c r="F17" t="s">
+        <v>483</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>106559</v>
+      </c>
+      <c r="C18" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D18" t="s">
+        <v>304</v>
+      </c>
+      <c r="E18" t="s">
+        <v>305</v>
+      </c>
+      <c r="F18" t="s">
+        <v>306</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>106559</v>
+      </c>
+      <c r="C19" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E19" t="s">
+        <v>465</v>
+      </c>
+      <c r="F19" t="s">
+        <v>466</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>106559</v>
+      </c>
+      <c r="C20" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D20" t="s">
+        <v>259</v>
+      </c>
+      <c r="E20" t="s">
+        <v>260</v>
+      </c>
+      <c r="F20" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>106559</v>
+      </c>
+      <c r="C21" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D21" t="s">
+        <v>467</v>
+      </c>
+      <c r="E21" t="s">
+        <v>468</v>
+      </c>
+      <c r="F21" t="s">
+        <v>469</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>106559</v>
+      </c>
+      <c r="C22" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>106559</v>
+      </c>
+      <c r="C23" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D23" t="s">
+        <v>503</v>
+      </c>
+      <c r="E23" t="s">
+        <v>504</v>
+      </c>
+      <c r="F23" t="s">
+        <v>505</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>106559</v>
+      </c>
+      <c r="C24" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D24" t="s">
+        <v>307</v>
+      </c>
+      <c r="E24" t="s">
+        <v>308</v>
+      </c>
+      <c r="F24" t="s">
+        <v>309</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>106559</v>
+      </c>
+      <c r="C25" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D25" t="s">
+        <v>310</v>
+      </c>
+      <c r="E25" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" t="s">
+        <v>312</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>106559</v>
+      </c>
+      <c r="C26" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D26" t="s">
+        <v>500</v>
+      </c>
+      <c r="E26" t="s">
+        <v>501</v>
+      </c>
+      <c r="F26" t="s">
+        <v>502</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>106559</v>
+      </c>
+      <c r="C27" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D27" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>106559</v>
+      </c>
+      <c r="C28" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D28" t="s">
+        <v>484</v>
+      </c>
+      <c r="E28" t="s">
+        <v>485</v>
+      </c>
+      <c r="F28" t="s">
+        <v>486</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>106559</v>
+      </c>
+      <c r="C29" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D29" t="s">
+        <v>414</v>
+      </c>
+      <c r="E29" t="s">
+        <v>415</v>
+      </c>
+      <c r="F29" t="s">
+        <v>416</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>106559</v>
+      </c>
+      <c r="C30" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D30" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>106559</v>
+      </c>
+      <c r="C31" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D31" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" t="s">
+        <v>315</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>106559</v>
+      </c>
+      <c r="C32" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D32" t="s">
+        <v>397</v>
+      </c>
+      <c r="E32" t="s">
+        <v>398</v>
+      </c>
+      <c r="F32" t="s">
+        <v>399</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>106559</v>
+      </c>
+      <c r="C33" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D33" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33" t="s">
+        <v>272</v>
+      </c>
+      <c r="F33" t="s">
+        <v>273</v>
+      </c>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>106559</v>
+      </c>
+      <c r="C34" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D34" t="s">
+        <v>436</v>
+      </c>
+      <c r="E34" t="s">
+        <v>437</v>
+      </c>
+      <c r="F34" t="s">
+        <v>438</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>106559</v>
+      </c>
+      <c r="C35" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>106559</v>
+      </c>
+      <c r="C36" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>106559</v>
+      </c>
+      <c r="C37" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D37" t="s">
+        <v>274</v>
+      </c>
+      <c r="E37" t="s">
+        <v>275</v>
+      </c>
+      <c r="F37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>106559</v>
+      </c>
+      <c r="C38" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>106559</v>
+      </c>
+      <c r="C39" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" t="s">
+        <v>233</v>
+      </c>
+      <c r="F39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>106559</v>
+      </c>
+      <c r="C40" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D40" t="s">
+        <v>360</v>
+      </c>
+      <c r="E40" t="s">
+        <v>361</v>
+      </c>
+      <c r="F40" t="s">
+        <v>362</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>106559</v>
+      </c>
+      <c r="C41" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>106559</v>
+      </c>
+      <c r="C42" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" t="s">
+        <v>106</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>106559</v>
+      </c>
+      <c r="C43" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D43" t="s">
+        <v>316</v>
+      </c>
+      <c r="E43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F43" t="s">
+        <v>318</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>106559</v>
+      </c>
+      <c r="C44" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>106559</v>
+      </c>
+      <c r="C45" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>106559</v>
+      </c>
+      <c r="C46" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>106559</v>
+      </c>
+      <c r="C47" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D47" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>106559</v>
+      </c>
+      <c r="C48" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D48" t="s">
+        <v>487</v>
+      </c>
+      <c r="E48" t="s">
+        <v>488</v>
+      </c>
+      <c r="F48" t="s">
+        <v>489</v>
+      </c>
+      <c r="G48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>106559</v>
+      </c>
+      <c r="C49" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D49" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>106559</v>
+      </c>
+      <c r="C50" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D50" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>106559</v>
+      </c>
+      <c r="C51" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D51" t="s">
+        <v>439</v>
+      </c>
+      <c r="E51" t="s">
+        <v>440</v>
+      </c>
+      <c r="F51" t="s">
+        <v>441</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>106559</v>
+      </c>
+      <c r="C52" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D52" t="s">
+        <v>400</v>
+      </c>
+      <c r="E52" t="s">
+        <v>401</v>
+      </c>
+      <c r="F52" t="s">
+        <v>402</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>106559</v>
+      </c>
+      <c r="C53" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D53" t="s">
+        <v>319</v>
+      </c>
+      <c r="E53" t="s">
+        <v>305</v>
+      </c>
+      <c r="F53" t="s">
+        <v>320</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>106559</v>
+      </c>
+      <c r="C54" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D54" t="s">
+        <v>277</v>
+      </c>
+      <c r="E54" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" t="s">
+        <v>279</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>106559</v>
+      </c>
+      <c r="C55" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>106559</v>
+      </c>
+      <c r="C56" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" t="s">
+        <v>172</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>106559</v>
+      </c>
+      <c r="C57" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D57" t="s">
+        <v>417</v>
+      </c>
+      <c r="E57" t="s">
+        <v>418</v>
+      </c>
+      <c r="F57" t="s">
+        <v>419</v>
+      </c>
+      <c r="G57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>106559</v>
+      </c>
+      <c r="C58" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D58" t="s">
+        <v>442</v>
+      </c>
+      <c r="E58" t="s">
+        <v>443</v>
+      </c>
+      <c r="F58" t="s">
+        <v>444</v>
+      </c>
+      <c r="G58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>106559</v>
+      </c>
+      <c r="C59" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D59" t="s">
+        <v>420</v>
+      </c>
+      <c r="E59" t="s">
+        <v>415</v>
+      </c>
+      <c r="F59" t="s">
+        <v>421</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>106559</v>
+      </c>
+      <c r="C60" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D60" t="s">
+        <v>217</v>
+      </c>
+      <c r="E60" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" t="s">
+        <v>219</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>106559</v>
+      </c>
+      <c r="C61" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D61" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" t="s">
+        <v>203</v>
+      </c>
+      <c r="F61" t="s">
+        <v>204</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>106559</v>
+      </c>
+      <c r="C62" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D62" t="s">
+        <v>321</v>
+      </c>
+      <c r="E62" t="s">
+        <v>322</v>
+      </c>
+      <c r="F62" t="s">
+        <v>323</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>106559</v>
+      </c>
+      <c r="C63" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>106559</v>
+      </c>
+      <c r="C64" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D64" t="s">
+        <v>324</v>
+      </c>
+      <c r="E64" t="s">
+        <v>325</v>
+      </c>
+      <c r="F64" t="s">
+        <v>326</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>106559</v>
+      </c>
+      <c r="C65" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>106559</v>
+      </c>
+      <c r="C66" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D66" t="s">
+        <v>173</v>
+      </c>
+      <c r="E66" t="s">
+        <v>174</v>
+      </c>
+      <c r="F66" t="s">
+        <v>175</v>
+      </c>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>106559</v>
+      </c>
+      <c r="C67" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D67" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" t="s">
+        <v>111</v>
+      </c>
+      <c r="F67" t="s">
+        <v>112</v>
+      </c>
+      <c r="G67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>106559</v>
+      </c>
+      <c r="C68" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D68" t="s">
+        <v>427</v>
+      </c>
+      <c r="E68" t="s">
+        <v>428</v>
+      </c>
+      <c r="F68" t="s">
+        <v>429</v>
+      </c>
+      <c r="G68" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>106559</v>
+      </c>
+      <c r="C69" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D69" t="s">
+        <v>490</v>
+      </c>
+      <c r="E69" t="s">
+        <v>491</v>
+      </c>
+      <c r="F69" t="s">
+        <v>492</v>
+      </c>
+      <c r="G69" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>106559</v>
+      </c>
+      <c r="C70" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D70" t="s">
+        <v>373</v>
+      </c>
+      <c r="E70" t="s">
+        <v>374</v>
+      </c>
+      <c r="F70" t="s">
+        <v>375</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>106559</v>
+      </c>
+      <c r="C71" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D71" t="s">
+        <v>238</v>
+      </c>
+      <c r="E71" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" t="s">
+        <v>240</v>
+      </c>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>106559</v>
+      </c>
+      <c r="C72" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D72" t="s">
+        <v>493</v>
+      </c>
+      <c r="E72" t="s">
+        <v>494</v>
+      </c>
+      <c r="F72" t="s">
+        <v>495</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>106559</v>
+      </c>
+      <c r="C73" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" t="s">
+        <v>49</v>
+      </c>
+      <c r="F73" t="s">
+        <v>50</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>106559</v>
+      </c>
+      <c r="C74" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D74" t="s">
+        <v>205</v>
+      </c>
+      <c r="E74" t="s">
+        <v>206</v>
+      </c>
+      <c r="F74" t="s">
+        <v>207</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>106559</v>
+      </c>
+      <c r="C75" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D75" t="s">
+        <v>445</v>
+      </c>
+      <c r="E75" t="s">
+        <v>446</v>
+      </c>
+      <c r="F75" t="s">
+        <v>447</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>106559</v>
+      </c>
+      <c r="C76" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D76" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" t="s">
+        <v>52</v>
+      </c>
+      <c r="F76" t="s">
+        <v>53</v>
+      </c>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>106559</v>
+      </c>
+      <c r="C77" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D77" t="s">
+        <v>448</v>
+      </c>
+      <c r="E77" t="s">
+        <v>449</v>
+      </c>
+      <c r="F77" t="s">
+        <v>450</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>106559</v>
+      </c>
+      <c r="C78" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D78" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" t="s">
+        <v>209</v>
+      </c>
+      <c r="F78" t="s">
+        <v>210</v>
+      </c>
+      <c r="G78" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>106559</v>
+      </c>
+      <c r="C79" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D79" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" t="s">
+        <v>143</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>106559</v>
+      </c>
+      <c r="C80" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D80" t="s">
+        <v>473</v>
+      </c>
+      <c r="E80" t="s">
+        <v>474</v>
+      </c>
+      <c r="F80" t="s">
+        <v>143</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>106559</v>
+      </c>
+      <c r="C81" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D81" t="s">
+        <v>187</v>
+      </c>
+      <c r="E81" t="s">
+        <v>188</v>
+      </c>
+      <c r="F81" t="s">
+        <v>189</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>106559</v>
+      </c>
+      <c r="C82" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D82" t="s">
+        <v>262</v>
+      </c>
+      <c r="E82" t="s">
+        <v>263</v>
+      </c>
+      <c r="F82" t="s">
+        <v>264</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>106559</v>
+      </c>
+      <c r="C83" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D83" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>56</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>106559</v>
+      </c>
+      <c r="C84" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D84" t="s">
+        <v>430</v>
+      </c>
+      <c r="E84" t="s">
+        <v>431</v>
+      </c>
+      <c r="F84" t="s">
+        <v>432</v>
+      </c>
+      <c r="G84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>106559</v>
+      </c>
+      <c r="C85" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D85" t="s">
+        <v>496</v>
+      </c>
+      <c r="E85" t="s">
+        <v>497</v>
+      </c>
+      <c r="F85" t="s">
+        <v>432</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>106559</v>
+      </c>
+      <c r="C86" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D86" t="s">
+        <v>220</v>
+      </c>
+      <c r="E86" t="s">
+        <v>221</v>
+      </c>
+      <c r="F86" t="s">
+        <v>222</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>106559</v>
+      </c>
+      <c r="C87" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D87" t="s">
+        <v>327</v>
+      </c>
+      <c r="E87" t="s">
+        <v>328</v>
+      </c>
+      <c r="F87" t="s">
+        <v>329</v>
+      </c>
+      <c r="G87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>106559</v>
+      </c>
+      <c r="C88" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D88" t="s">
+        <v>376</v>
+      </c>
+      <c r="E88" t="s">
+        <v>377</v>
+      </c>
+      <c r="F88" t="s">
+        <v>378</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>106559</v>
+      </c>
+      <c r="C89" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D89" t="s">
+        <v>190</v>
+      </c>
+      <c r="E89" t="s">
+        <v>191</v>
+      </c>
+      <c r="F89" t="s">
+        <v>192</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>106559</v>
+      </c>
+      <c r="C90" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D90" t="s">
+        <v>176</v>
+      </c>
+      <c r="E90" t="s">
+        <v>177</v>
+      </c>
+      <c r="F90" t="s">
+        <v>178</v>
+      </c>
+      <c r="G90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>106559</v>
+      </c>
+      <c r="C91" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D91" t="s">
+        <v>403</v>
+      </c>
+      <c r="E91" t="s">
+        <v>404</v>
+      </c>
+      <c r="F91" t="s">
+        <v>405</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>106559</v>
+      </c>
+      <c r="C92" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D92" t="s">
+        <v>385</v>
+      </c>
+      <c r="E92" t="s">
+        <v>386</v>
+      </c>
+      <c r="F92" t="s">
+        <v>387</v>
+      </c>
+      <c r="G92" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>106559</v>
+      </c>
+      <c r="C93" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D93" t="s">
+        <v>241</v>
+      </c>
+      <c r="E93" t="s">
+        <v>242</v>
+      </c>
+      <c r="F93" t="s">
+        <v>243</v>
+      </c>
+      <c r="G93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>106559</v>
+      </c>
+      <c r="C94" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D94" t="s">
+        <v>280</v>
+      </c>
+      <c r="E94" t="s">
+        <v>281</v>
+      </c>
+      <c r="F94" t="s">
+        <v>282</v>
+      </c>
+      <c r="G94" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>106559</v>
+      </c>
+      <c r="C95" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D95" t="s">
+        <v>330</v>
+      </c>
+      <c r="E95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>106559</v>
+      </c>
+      <c r="C96" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D96" t="s">
+        <v>433</v>
+      </c>
+      <c r="E96" t="s">
+        <v>434</v>
+      </c>
+      <c r="F96" t="s">
+        <v>435</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>106559</v>
+      </c>
+      <c r="C97" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D97" t="s">
+        <v>229</v>
+      </c>
+      <c r="E97" t="s">
+        <v>230</v>
+      </c>
+      <c r="F97" t="s">
+        <v>231</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>106559</v>
+      </c>
+      <c r="C98" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D98" t="s">
+        <v>57</v>
+      </c>
+      <c r="E98" t="s">
+        <v>58</v>
+      </c>
+      <c r="F98" t="s">
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>106559</v>
+      </c>
+      <c r="C99" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D99" t="s">
+        <v>283</v>
+      </c>
+      <c r="E99" t="s">
+        <v>284</v>
+      </c>
+      <c r="F99" t="s">
+        <v>285</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>106559</v>
+      </c>
+      <c r="C100" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D100" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" t="s">
+        <v>194</v>
+      </c>
+      <c r="F100" t="s">
+        <v>195</v>
+      </c>
+      <c r="G100" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>106559</v>
+      </c>
+      <c r="C101" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D101" t="s">
+        <v>60</v>
+      </c>
+      <c r="E101" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" t="s">
+        <v>62</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>106559</v>
+      </c>
+      <c r="C102" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D102" t="s">
+        <v>451</v>
+      </c>
+      <c r="E102" t="s">
+        <v>452</v>
+      </c>
+      <c r="F102" t="s">
+        <v>453</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>106559</v>
+      </c>
+      <c r="C103" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D103" t="s">
+        <v>454</v>
+      </c>
+      <c r="E103" t="s">
+        <v>455</v>
+      </c>
+      <c r="F103" t="s">
+        <v>456</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>106559</v>
+      </c>
+      <c r="C104" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D104" t="s">
+        <v>470</v>
+      </c>
+      <c r="E104" t="s">
+        <v>471</v>
+      </c>
+      <c r="F104" t="s">
+        <v>472</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>106559</v>
+      </c>
+      <c r="C105" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D105" t="s">
+        <v>244</v>
+      </c>
+      <c r="E105" t="s">
+        <v>245</v>
+      </c>
+      <c r="F105" t="s">
+        <v>246</v>
+      </c>
+      <c r="G105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>106559</v>
+      </c>
+      <c r="C106" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D106" t="s">
+        <v>333</v>
+      </c>
+      <c r="E106" t="s">
+        <v>334</v>
+      </c>
+      <c r="F106" t="s">
+        <v>335</v>
+      </c>
+      <c r="G106" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>106559</v>
+      </c>
+      <c r="C107" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D107" t="s">
+        <v>196</v>
+      </c>
+      <c r="E107" t="s">
+        <v>197</v>
+      </c>
+      <c r="F107" t="s">
+        <v>198</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>106559</v>
+      </c>
+      <c r="C108" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D108" t="s">
+        <v>247</v>
+      </c>
+      <c r="E108" t="s">
+        <v>248</v>
+      </c>
+      <c r="F108" t="s">
+        <v>249</v>
+      </c>
+      <c r="G108" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>106559</v>
+      </c>
+      <c r="C109" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D109" t="s">
+        <v>113</v>
+      </c>
+      <c r="E109" t="s">
+        <v>114</v>
+      </c>
+      <c r="F109" t="s">
+        <v>115</v>
+      </c>
+      <c r="G109" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>106559</v>
+      </c>
+      <c r="C110" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D110" t="s">
+        <v>286</v>
+      </c>
+      <c r="E110" t="s">
+        <v>287</v>
+      </c>
+      <c r="F110" t="s">
+        <v>288</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>106559</v>
+      </c>
+      <c r="C111" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D111" t="s">
+        <v>116</v>
+      </c>
+      <c r="E111" t="s">
+        <v>99</v>
+      </c>
+      <c r="F111" t="s">
+        <v>117</v>
+      </c>
+      <c r="G111" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>106559</v>
+      </c>
+      <c r="C112" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D112" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112" t="s">
+        <v>64</v>
+      </c>
+      <c r="F112" t="s">
+        <v>65</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>106559</v>
+      </c>
+      <c r="C113" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D113" t="s">
+        <v>422</v>
+      </c>
+      <c r="E113" t="s">
+        <v>423</v>
+      </c>
+      <c r="F113" t="s">
+        <v>424</v>
+      </c>
+      <c r="G113" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>106559</v>
+      </c>
+      <c r="C114" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D114" t="s">
+        <v>92</v>
+      </c>
+      <c r="E114" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" t="s">
+        <v>94</v>
+      </c>
+      <c r="G114" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>106559</v>
+      </c>
+      <c r="C115" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D115" t="s">
+        <v>66</v>
+      </c>
+      <c r="E115" t="s">
+        <v>67</v>
+      </c>
+      <c r="F115" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>106559</v>
+      </c>
+      <c r="C116" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E116" t="s">
+        <v>145</v>
+      </c>
+      <c r="F116" t="s">
+        <v>146</v>
+      </c>
+      <c r="G116" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>106559</v>
+      </c>
+      <c r="C117" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D117" t="s">
+        <v>363</v>
+      </c>
+      <c r="E117" t="s">
+        <v>364</v>
+      </c>
+      <c r="F117" t="s">
+        <v>365</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>106559</v>
+      </c>
+      <c r="C118" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D118" t="s">
+        <v>336</v>
+      </c>
+      <c r="E118" t="s">
+        <v>337</v>
+      </c>
+      <c r="F118" t="s">
+        <v>338</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>106559</v>
+      </c>
+      <c r="C119" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F119" t="s">
+        <v>71</v>
+      </c>
+      <c r="G119" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>106559</v>
+      </c>
+      <c r="C120" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D120" t="s">
+        <v>118</v>
+      </c>
+      <c r="E120" t="s">
+        <v>119</v>
+      </c>
+      <c r="F120" t="s">
+        <v>120</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>106559</v>
+      </c>
+      <c r="C121" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D121" t="s">
+        <v>366</v>
+      </c>
+      <c r="E121" t="s">
+        <v>364</v>
+      </c>
+      <c r="F121" t="s">
+        <v>367</v>
+      </c>
+      <c r="G121" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>106559</v>
+      </c>
+      <c r="C122" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D122" t="s">
+        <v>72</v>
+      </c>
+      <c r="E122" t="s">
+        <v>73</v>
+      </c>
+      <c r="F122" t="s">
+        <v>74</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>106559</v>
+      </c>
+      <c r="C123" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D123" t="s">
+        <v>179</v>
+      </c>
+      <c r="E123" t="s">
+        <v>156</v>
+      </c>
+      <c r="F123" t="s">
+        <v>180</v>
+      </c>
+      <c r="G123" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>106559</v>
+      </c>
+      <c r="C124" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D124" t="s">
+        <v>292</v>
+      </c>
+      <c r="E124" t="s">
+        <v>293</v>
+      </c>
+      <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>106559</v>
+      </c>
+      <c r="C125" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D125" t="s">
+        <v>155</v>
+      </c>
+      <c r="E125" t="s">
+        <v>156</v>
+      </c>
+      <c r="F125" t="s">
+        <v>157</v>
+      </c>
+      <c r="G125" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>106559</v>
+      </c>
+      <c r="C126" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D126" t="s">
+        <v>121</v>
+      </c>
+      <c r="E126" t="s">
+        <v>122</v>
+      </c>
+      <c r="F126" t="s">
+        <v>123</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <v>106559</v>
+      </c>
+      <c r="C127" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D127" t="s">
+        <v>406</v>
+      </c>
+      <c r="E127" t="s">
+        <v>404</v>
+      </c>
+      <c r="F127" t="s">
+        <v>407</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <v>106559</v>
+      </c>
+      <c r="C128" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D128" t="s">
+        <v>457</v>
+      </c>
+      <c r="E128" t="s">
+        <v>452</v>
+      </c>
+      <c r="F128" t="s">
+        <v>458</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <v>106559</v>
+      </c>
+      <c r="C129" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D129" t="s">
+        <v>425</v>
+      </c>
+      <c r="E129" t="s">
+        <v>415</v>
+      </c>
+      <c r="F129" t="s">
+        <v>426</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>106559</v>
+      </c>
+      <c r="C130" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D130" t="s">
+        <v>250</v>
+      </c>
+      <c r="E130" t="s">
+        <v>251</v>
+      </c>
+      <c r="F130" t="s">
+        <v>252</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>106559</v>
+      </c>
+      <c r="C131" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D131" t="s">
+        <v>459</v>
+      </c>
+      <c r="E131" t="s">
+        <v>452</v>
+      </c>
+      <c r="F131" t="s">
+        <v>460</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>106559</v>
+      </c>
+      <c r="C132" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D132" t="s">
+        <v>368</v>
+      </c>
+      <c r="E132" t="s">
+        <v>361</v>
+      </c>
+      <c r="F132" t="s">
+        <v>369</v>
+      </c>
+      <c r="G132" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>106559</v>
+      </c>
+      <c r="C133" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D133" t="s">
+        <v>339</v>
+      </c>
+      <c r="E133" t="s">
+        <v>340</v>
+      </c>
+      <c r="F133" t="s">
+        <v>341</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>106559</v>
+      </c>
+      <c r="C134" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D134" t="s">
+        <v>388</v>
+      </c>
+      <c r="E134" t="s">
+        <v>389</v>
+      </c>
+      <c r="F134" t="s">
+        <v>390</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>106559</v>
+      </c>
+      <c r="C135" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D135" t="s">
+        <v>379</v>
+      </c>
+      <c r="E135" t="s">
+        <v>380</v>
+      </c>
+      <c r="F135" t="s">
+        <v>381</v>
+      </c>
+      <c r="G135" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>106559</v>
+      </c>
+      <c r="C136" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D136" t="s">
+        <v>181</v>
+      </c>
+      <c r="E136" t="s">
+        <v>182</v>
+      </c>
+      <c r="F136" t="s">
+        <v>183</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A137">
+        <v>106559</v>
+      </c>
+      <c r="C137" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D137" t="s">
+        <v>370</v>
+      </c>
+      <c r="E137" t="s">
+        <v>371</v>
+      </c>
+      <c r="F137" t="s">
+        <v>372</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A138">
+        <v>106559</v>
+      </c>
+      <c r="C138" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D138" t="s">
+        <v>461</v>
+      </c>
+      <c r="E138" t="s">
+        <v>462</v>
+      </c>
+      <c r="F138" t="s">
+        <v>463</v>
+      </c>
+      <c r="G138" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A139">
+        <v>106559</v>
+      </c>
+      <c r="C139" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D139" t="s">
+        <v>75</v>
+      </c>
+      <c r="E139" t="s">
+        <v>76</v>
+      </c>
+      <c r="F139" t="s">
+        <v>77</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A140">
+        <v>106559</v>
+      </c>
+      <c r="C140" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D140" t="s">
+        <v>295</v>
+      </c>
+      <c r="E140" t="s">
+        <v>296</v>
+      </c>
+      <c r="F140" t="s">
+        <v>297</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A141">
+        <v>106559</v>
+      </c>
+      <c r="C141" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D141" t="s">
+        <v>124</v>
+      </c>
+      <c r="E141" t="s">
+        <v>125</v>
+      </c>
+      <c r="F141" t="s">
+        <v>126</v>
+      </c>
+      <c r="G141" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A142">
+        <v>106559</v>
+      </c>
+      <c r="C142" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D142" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" t="s">
+        <v>224</v>
+      </c>
+      <c r="F142" t="s">
+        <v>225</v>
+      </c>
+      <c r="G142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A143">
+        <v>106559</v>
+      </c>
+      <c r="C143" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D143" t="s">
+        <v>127</v>
+      </c>
+      <c r="E143" t="s">
+        <v>125</v>
+      </c>
+      <c r="F143" t="s">
+        <v>128</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A144">
+        <v>106559</v>
+      </c>
+      <c r="C144" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D144" t="s">
+        <v>147</v>
+      </c>
+      <c r="E144" t="s">
+        <v>148</v>
+      </c>
+      <c r="F144" t="s">
+        <v>149</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A145">
+        <v>106559</v>
+      </c>
+      <c r="C145" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D145" t="s">
+        <v>184</v>
+      </c>
+      <c r="E145" t="s">
+        <v>185</v>
+      </c>
+      <c r="F145" t="s">
+        <v>186</v>
+      </c>
+      <c r="G145" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A146">
+        <v>106559</v>
+      </c>
+      <c r="C146" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D146" t="s">
+        <v>253</v>
+      </c>
+      <c r="E146" t="s">
+        <v>254</v>
+      </c>
+      <c r="F146" t="s">
+        <v>255</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A147">
+        <v>106559</v>
+      </c>
+      <c r="C147" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D147" t="s">
+        <v>211</v>
+      </c>
+      <c r="E147" t="s">
+        <v>212</v>
+      </c>
+      <c r="F147" t="s">
+        <v>213</v>
+      </c>
+      <c r="G147" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148">
+        <v>106559</v>
+      </c>
+      <c r="C148" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D148" t="s">
+        <v>289</v>
+      </c>
+      <c r="E148" t="s">
+        <v>290</v>
+      </c>
+      <c r="F148" t="s">
+        <v>291</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A149">
+        <v>106559</v>
+      </c>
+      <c r="C149" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D149" t="s">
+        <v>150</v>
+      </c>
+      <c r="E149" t="s">
+        <v>145</v>
+      </c>
+      <c r="F149" t="s">
+        <v>151</v>
+      </c>
+      <c r="G149" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A150">
+        <v>106559</v>
+      </c>
+      <c r="C150" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D150" t="s">
+        <v>265</v>
+      </c>
+      <c r="E150" t="s">
+        <v>266</v>
+      </c>
+      <c r="F150" t="s">
+        <v>267</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A151">
+        <v>106559</v>
+      </c>
+      <c r="C151" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D151" t="s">
+        <v>298</v>
+      </c>
+      <c r="E151" t="s">
+        <v>299</v>
+      </c>
+      <c r="F151" t="s">
+        <v>300</v>
+      </c>
+      <c r="G151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A152">
+        <v>106559</v>
+      </c>
+      <c r="C152" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D152" t="s">
+        <v>129</v>
+      </c>
+      <c r="E152" t="s">
+        <v>130</v>
+      </c>
+      <c r="F152" t="s">
+        <v>131</v>
+      </c>
+      <c r="G152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A153">
+        <v>106559</v>
+      </c>
+      <c r="C153" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D153" t="s">
+        <v>391</v>
+      </c>
+      <c r="E153" t="s">
+        <v>392</v>
+      </c>
+      <c r="F153" t="s">
+        <v>393</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A154">
+        <v>106559</v>
+      </c>
+      <c r="C154" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D154" t="s">
+        <v>78</v>
+      </c>
+      <c r="E154" t="s">
+        <v>70</v>
+      </c>
+      <c r="F154" t="s">
+        <v>79</v>
+      </c>
+      <c r="G154" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A155">
+        <v>106559</v>
+      </c>
+      <c r="C155" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D155" t="s">
+        <v>132</v>
+      </c>
+      <c r="E155" t="s">
+        <v>133</v>
+      </c>
+      <c r="F155" t="s">
+        <v>134</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A156">
+        <v>106559</v>
+      </c>
+      <c r="C156" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D156" t="s">
+        <v>80</v>
+      </c>
+      <c r="E156" t="s">
+        <v>81</v>
+      </c>
+      <c r="F156" t="s">
+        <v>82</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A157">
+        <v>106559</v>
+      </c>
+      <c r="C157" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D157" t="s">
+        <v>135</v>
+      </c>
+      <c r="E157" t="s">
+        <v>136</v>
+      </c>
+      <c r="F157" t="s">
+        <v>137</v>
+      </c>
+      <c r="G157" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A158">
+        <v>106559</v>
+      </c>
+      <c r="C158" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D158" t="s">
+        <v>83</v>
+      </c>
+      <c r="E158" t="s">
+        <v>84</v>
+      </c>
+      <c r="F158" t="s">
+        <v>85</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A159">
+        <v>106559</v>
+      </c>
+      <c r="C159" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D159" t="s">
+        <v>152</v>
+      </c>
+      <c r="E159" t="s">
+        <v>153</v>
+      </c>
+      <c r="F159" t="s">
+        <v>154</v>
+      </c>
+      <c r="G159" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A160">
+        <v>106559</v>
+      </c>
+      <c r="C160" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D160" t="s">
+        <v>498</v>
+      </c>
+      <c r="E160" t="s">
+        <v>499</v>
+      </c>
+      <c r="F160" t="s">
+        <v>154</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A161">
+        <v>106559</v>
+      </c>
+      <c r="C161" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D161" t="s">
+        <v>214</v>
+      </c>
+      <c r="E161" t="s">
+        <v>215</v>
+      </c>
+      <c r="F161" t="s">
+        <v>216</v>
+      </c>
+      <c r="G161" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A162">
+        <v>106559</v>
+      </c>
+      <c r="C162" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D162" t="s">
+        <v>408</v>
+      </c>
+      <c r="E162" t="s">
+        <v>409</v>
+      </c>
+      <c r="F162" t="s">
+        <v>410</v>
+      </c>
+      <c r="G162" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A163">
+        <v>106559</v>
+      </c>
+      <c r="C163" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D163" t="s">
+        <v>475</v>
+      </c>
+      <c r="E163" t="s">
+        <v>476</v>
+      </c>
+      <c r="F163" t="s">
+        <v>477</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A164">
+        <v>106559</v>
+      </c>
+      <c r="C164" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D164" t="s">
+        <v>342</v>
+      </c>
+      <c r="E164" t="s">
+        <v>343</v>
+      </c>
+      <c r="F164" t="s">
+        <v>344</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A165">
+        <v>106559</v>
+      </c>
+      <c r="C165" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D165" t="s">
+        <v>345</v>
+      </c>
+      <c r="E165" t="s">
+        <v>346</v>
+      </c>
+      <c r="F165" t="s">
+        <v>347</v>
+      </c>
+      <c r="G165" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A166">
+        <v>106559</v>
+      </c>
+      <c r="C166" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D166" t="s">
+        <v>394</v>
+      </c>
+      <c r="E166" t="s">
+        <v>395</v>
+      </c>
+      <c r="F166" t="s">
+        <v>396</v>
+      </c>
+      <c r="G166" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A167">
+        <v>106559</v>
+      </c>
+      <c r="C167" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D167" t="s">
+        <v>348</v>
+      </c>
+      <c r="E167" t="s">
+        <v>349</v>
+      </c>
+      <c r="F167" t="s">
+        <v>350</v>
+      </c>
+      <c r="G167" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A168">
+        <v>106559</v>
+      </c>
+      <c r="C168" s="10">
+        <v>45988</v>
+      </c>
+      <c r="D168" t="s">
+        <v>351</v>
+      </c>
+      <c r="E168" t="s">
+        <v>352</v>
+      </c>
+      <c r="F168" t="s">
+        <v>353</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>